--- a/logs/IPhone16e_fixed-point.xlsx
+++ b/logs/IPhone16e_fixed-point.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\so0ojung\Desktop\boston_field_251106\logs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\so0ojung\Downloads\nr-field-analysis-master_1110\logs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1569FAF8-B1BB-4C76-9607-E32AC4B7631E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34E1C6F1-8DF4-49BD-8695-62B7C2EB884B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="8040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="622" uniqueCount="51">
   <si>
     <t>PDSCH ACK Tput MIN</t>
   </si>
@@ -112,58 +112,79 @@
     <t>towerside</t>
   </si>
   <si>
-    <t>t1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <t>busstop2</t>
   </si>
   <si>
-    <t>t2</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <t>deungsanro2</t>
   </si>
   <si>
-    <t>t3</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <t>deungsanro3</t>
   </si>
   <si>
-    <t>t4</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <t>deungsanro4</t>
   </si>
   <si>
-    <t>t5</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <t>deungsanro5</t>
   </si>
   <si>
-    <t>LAT</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <t>deungsanro</t>
   </si>
   <si>
-    <t>LON</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <t>gongwon2</t>
   </si>
   <si>
-    <t>Location</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Frequency</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Date</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Base Station</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Test Num</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <t>Lon</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>Huam345-5</t>
   </si>
   <si>
     <t>Namsan</t>
+  </si>
+  <si>
+    <t>Location</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Frequency</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Date</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Base Station</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>t1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>t2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>t3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>t4</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>t5</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Test Num</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LAT</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -186,17 +207,17 @@
       <charset val="129"/>
     </font>
     <font>
-      <sz val="11"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
       <sz val="8"/>
       <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
     <font>
       <b/>
@@ -216,7 +237,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -241,6 +262,17 @@
     </border>
     <border>
       <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right/>
       <top/>
       <bottom style="thin">
@@ -252,14 +284,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -563,36 +596,39 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V81"/>
+  <dimension ref="A1:V151"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="3" width="12.08203125" customWidth="1"/>
-    <col min="4" max="4" width="20.08203125" customWidth="1"/>
-    <col min="5" max="7" width="12.08203125" customWidth="1"/>
-    <col min="9" max="9" width="13.1640625" customWidth="1"/>
+    <col min="1" max="1" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.08203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.58203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.25" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A1" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F1" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="E1" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>41</v>
+      <c r="G1" s="4" t="s">
+        <v>49</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>0</v>
@@ -642,7 +678,7 @@
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B2" s="2">
         <v>251104</v>
@@ -710,7 +746,7 @@
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B3" s="2">
         <v>251104</v>
@@ -769,7 +805,7 @@
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B4" s="2">
         <v>251104</v>
@@ -837,7 +873,7 @@
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B5" s="2">
         <v>251104</v>
@@ -896,7 +932,7 @@
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B6" s="2">
         <v>251104</v>
@@ -964,7 +1000,7 @@
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A7" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B7" s="2">
         <v>251104</v>
@@ -1032,7 +1068,7 @@
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A8" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B8" s="2">
         <v>251104</v>
@@ -1100,7 +1136,7 @@
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A9" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B9" s="2">
         <v>251104</v>
@@ -1168,7 +1204,7 @@
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A10" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B10" s="2">
         <v>251104</v>
@@ -1236,7 +1272,7 @@
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A11" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B11" s="2">
         <v>251104</v>
@@ -1304,7 +1340,7 @@
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A12" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B12" s="2">
         <v>251104</v>
@@ -1372,7 +1408,7 @@
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A13" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B13" s="2">
         <v>251104</v>
@@ -1440,7 +1476,7 @@
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A14" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B14" s="2">
         <v>251104</v>
@@ -1508,7 +1544,7 @@
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A15" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B15" s="2">
         <v>251104</v>
@@ -1576,7 +1612,7 @@
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A16" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B16" s="2">
         <v>251104</v>
@@ -1644,7 +1680,7 @@
     </row>
     <row r="17" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A17" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B17" s="2">
         <v>251104</v>
@@ -1662,7 +1698,7 @@
         <v>126.98168</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="H17">
         <v>87.37</v>
@@ -1712,7 +1748,7 @@
     </row>
     <row r="18" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A18" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B18" s="2">
         <v>251104</v>
@@ -1730,7 +1766,7 @@
         <v>126.98168</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="H18">
         <v>82.07</v>
@@ -1780,7 +1816,7 @@
     </row>
     <row r="19" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A19" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B19" s="2">
         <v>251104</v>
@@ -1798,7 +1834,7 @@
         <v>126.98168</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="H19">
         <v>88.48</v>
@@ -1848,7 +1884,7 @@
     </row>
     <row r="20" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A20" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B20" s="2">
         <v>251104</v>
@@ -1866,7 +1902,7 @@
         <v>126.98168</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="H20">
         <v>86.35</v>
@@ -1916,7 +1952,7 @@
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A21" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B21" s="2">
         <v>251104</v>
@@ -1934,7 +1970,7 @@
         <v>126.98168</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="H21">
         <v>80.77</v>
@@ -1984,7 +2020,7 @@
     </row>
     <row r="22" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A22" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B22" s="2">
         <v>251104</v>
@@ -2052,7 +2088,7 @@
     </row>
     <row r="23" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A23" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B23" s="2">
         <v>251104</v>
@@ -2120,7 +2156,7 @@
     </row>
     <row r="24" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A24" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B24" s="2">
         <v>251104</v>
@@ -2188,7 +2224,7 @@
     </row>
     <row r="25" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A25" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B25" s="2">
         <v>251104</v>
@@ -2256,7 +2292,7 @@
     </row>
     <row r="26" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A26" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B26" s="2">
         <v>251104</v>
@@ -2324,7 +2360,7 @@
     </row>
     <row r="27" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A27" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B27" s="2">
         <v>251104</v>
@@ -2392,7 +2428,7 @@
     </row>
     <row r="28" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A28" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B28" s="2">
         <v>251104</v>
@@ -2460,7 +2496,7 @@
     </row>
     <row r="29" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A29" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B29" s="2">
         <v>251104</v>
@@ -2528,7 +2564,7 @@
     </row>
     <row r="30" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A30" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B30" s="2">
         <v>251104</v>
@@ -2596,7 +2632,7 @@
     </row>
     <row r="31" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A31" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B31" s="2">
         <v>251104</v>
@@ -2664,7 +2700,7 @@
     </row>
     <row r="32" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A32" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B32" s="2">
         <v>251104</v>
@@ -2732,7 +2768,7 @@
     </row>
     <row r="33" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A33" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B33" s="2">
         <v>251104</v>
@@ -2800,7 +2836,7 @@
     </row>
     <row r="34" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A34" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B34" s="2">
         <v>251104</v>
@@ -2868,7 +2904,7 @@
     </row>
     <row r="35" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A35" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B35" s="2">
         <v>251104</v>
@@ -2936,7 +2972,7 @@
     </row>
     <row r="36" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A36" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B36" s="2">
         <v>251104</v>
@@ -3004,7 +3040,7 @@
     </row>
     <row r="37" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A37" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B37" s="2">
         <v>251104</v>
@@ -3072,7 +3108,7 @@
     </row>
     <row r="38" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A38" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B38" s="2">
         <v>251104</v>
@@ -3140,7 +3176,7 @@
     </row>
     <row r="39" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A39" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B39" s="2">
         <v>251104</v>
@@ -3208,7 +3244,7 @@
     </row>
     <row r="40" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A40" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B40" s="2">
         <v>251104</v>
@@ -3276,7 +3312,7 @@
     </row>
     <row r="41" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A41" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B41" s="2">
         <v>251104</v>
@@ -3344,7 +3380,7 @@
     </row>
     <row r="42" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A42" s="2" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B42" s="2">
         <v>251106</v>
@@ -3412,7 +3448,7 @@
     </row>
     <row r="43" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A43" s="2" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B43" s="2">
         <v>251106</v>
@@ -3480,7 +3516,7 @@
     </row>
     <row r="44" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A44" s="2" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B44" s="2">
         <v>251106</v>
@@ -3548,7 +3584,7 @@
     </row>
     <row r="45" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A45" s="2" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B45" s="2">
         <v>251106</v>
@@ -3616,7 +3652,7 @@
     </row>
     <row r="46" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A46" s="2" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B46" s="2">
         <v>251106</v>
@@ -3684,7 +3720,7 @@
     </row>
     <row r="47" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A47" s="2" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B47" s="2">
         <v>251106</v>
@@ -3752,7 +3788,7 @@
     </row>
     <row r="48" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A48" s="2" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B48" s="2">
         <v>251106</v>
@@ -3820,7 +3856,7 @@
     </row>
     <row r="49" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A49" s="2" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B49" s="2">
         <v>251106</v>
@@ -3888,7 +3924,7 @@
     </row>
     <row r="50" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A50" s="2" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B50" s="2">
         <v>251106</v>
@@ -3956,7 +3992,7 @@
     </row>
     <row r="51" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A51" s="2" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B51" s="2">
         <v>251106</v>
@@ -4024,7 +4060,7 @@
     </row>
     <row r="52" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A52" s="2" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B52" s="2">
         <v>251106</v>
@@ -4092,7 +4128,7 @@
     </row>
     <row r="53" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A53" s="2" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B53" s="2">
         <v>251106</v>
@@ -4160,7 +4196,7 @@
     </row>
     <row r="54" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A54" s="2" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B54" s="2">
         <v>251106</v>
@@ -4228,7 +4264,7 @@
     </row>
     <row r="55" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A55" s="2" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B55" s="2">
         <v>251106</v>
@@ -4296,7 +4332,7 @@
     </row>
     <row r="56" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A56" s="2" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B56" s="2">
         <v>251106</v>
@@ -4364,7 +4400,7 @@
     </row>
     <row r="57" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A57" s="2" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B57" s="2">
         <v>251106</v>
@@ -4432,7 +4468,7 @@
     </row>
     <row r="58" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A58" s="2" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B58" s="2">
         <v>251106</v>
@@ -4500,7 +4536,7 @@
     </row>
     <row r="59" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A59" s="2" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B59" s="2">
         <v>251106</v>
@@ -4568,7 +4604,7 @@
     </row>
     <row r="60" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A60" s="2" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B60" s="2">
         <v>251106</v>
@@ -4636,7 +4672,7 @@
     </row>
     <row r="61" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A61" s="2" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B61" s="2">
         <v>251106</v>
@@ -4704,7 +4740,7 @@
     </row>
     <row r="62" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A62" s="2" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B62" s="2">
         <v>251106</v>
@@ -4772,7 +4808,7 @@
     </row>
     <row r="63" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A63" s="2" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B63" s="2">
         <v>251106</v>
@@ -4840,7 +4876,7 @@
     </row>
     <row r="64" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A64" s="2" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B64" s="2">
         <v>251106</v>
@@ -4908,7 +4944,7 @@
     </row>
     <row r="65" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A65" s="2" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B65" s="2">
         <v>251106</v>
@@ -4976,7 +5012,7 @@
     </row>
     <row r="66" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A66" s="2" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B66" s="2">
         <v>251106</v>
@@ -5044,7 +5080,7 @@
     </row>
     <row r="67" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A67" s="2" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B67" s="2">
         <v>251106</v>
@@ -5112,7 +5148,7 @@
     </row>
     <row r="68" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A68" s="2" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B68" s="2">
         <v>251106</v>
@@ -5180,7 +5216,7 @@
     </row>
     <row r="69" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A69" s="2" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B69" s="2">
         <v>251106</v>
@@ -5248,7 +5284,7 @@
     </row>
     <row r="70" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A70" s="2" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B70" s="2">
         <v>251106</v>
@@ -5316,7 +5352,7 @@
     </row>
     <row r="71" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A71" s="2" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B71" s="2">
         <v>251106</v>
@@ -5384,7 +5420,7 @@
     </row>
     <row r="72" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A72" s="2" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B72" s="2">
         <v>251106</v>
@@ -5452,7 +5488,7 @@
     </row>
     <row r="73" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A73" s="2" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B73" s="2">
         <v>251106</v>
@@ -5520,7 +5556,7 @@
     </row>
     <row r="74" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A74" s="2" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B74" s="2">
         <v>251106</v>
@@ -5588,7 +5624,7 @@
     </row>
     <row r="75" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A75" s="2" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B75" s="2">
         <v>251106</v>
@@ -5656,7 +5692,7 @@
     </row>
     <row r="76" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A76" s="2" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B76" s="2">
         <v>251106</v>
@@ -5724,7 +5760,7 @@
     </row>
     <row r="77" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A77" s="2" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B77" s="2">
         <v>251106</v>
@@ -5792,7 +5828,7 @@
     </row>
     <row r="78" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A78" s="2" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B78" s="2">
         <v>251106</v>
@@ -5860,7 +5896,7 @@
     </row>
     <row r="79" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A79" s="2" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B79" s="2">
         <v>251106</v>
@@ -5928,7 +5964,7 @@
     </row>
     <row r="80" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A80" s="2" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B80" s="2">
         <v>251106</v>
@@ -5996,7 +6032,7 @@
     </row>
     <row r="81" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A81" s="2" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B81" s="2">
         <v>251106</v>
@@ -6062,8 +6098,4768 @@
         <v>23.14</v>
       </c>
     </row>
+    <row r="82" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A82" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B82" s="2">
+        <v>251107</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E82" s="2">
+        <v>37.550910000000002</v>
+      </c>
+      <c r="F82" s="2">
+        <v>126.99139</v>
+      </c>
+      <c r="G82" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H82">
+        <v>34.03</v>
+      </c>
+      <c r="I82">
+        <v>49.9</v>
+      </c>
+      <c r="J82">
+        <v>43.77</v>
+      </c>
+      <c r="K82">
+        <v>31.38</v>
+      </c>
+      <c r="L82">
+        <v>49.9</v>
+      </c>
+      <c r="M82">
+        <v>42.13</v>
+      </c>
+      <c r="N82">
+        <v>0</v>
+      </c>
+      <c r="O82">
+        <v>0</v>
+      </c>
+      <c r="P82">
+        <v>0</v>
+      </c>
+      <c r="Q82">
+        <v>0</v>
+      </c>
+      <c r="R82">
+        <v>0</v>
+      </c>
+      <c r="S82">
+        <v>0</v>
+      </c>
+      <c r="T82">
+        <v>0</v>
+      </c>
+      <c r="U82">
+        <v>0</v>
+      </c>
+      <c r="V82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A83" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B83" s="2">
+        <v>251107</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E83" s="2">
+        <v>37.550910000000002</v>
+      </c>
+      <c r="F83" s="2">
+        <v>126.99139</v>
+      </c>
+      <c r="G83" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H83">
+        <v>36.78</v>
+      </c>
+      <c r="I83">
+        <v>47.1</v>
+      </c>
+      <c r="J83">
+        <v>43.81</v>
+      </c>
+      <c r="K83">
+        <v>36.78</v>
+      </c>
+      <c r="L83">
+        <v>47.1</v>
+      </c>
+      <c r="M83">
+        <v>43.65</v>
+      </c>
+      <c r="N83">
+        <v>0</v>
+      </c>
+      <c r="O83">
+        <v>0</v>
+      </c>
+      <c r="P83">
+        <v>0</v>
+      </c>
+      <c r="Q83">
+        <v>0</v>
+      </c>
+      <c r="R83">
+        <v>0</v>
+      </c>
+      <c r="S83">
+        <v>0</v>
+      </c>
+      <c r="T83">
+        <v>0</v>
+      </c>
+      <c r="U83">
+        <v>0</v>
+      </c>
+      <c r="V83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A84" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B84" s="2">
+        <v>251107</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E84" s="2">
+        <v>37.550910000000002</v>
+      </c>
+      <c r="F84" s="2">
+        <v>126.99139</v>
+      </c>
+      <c r="G84" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H84">
+        <v>33.58</v>
+      </c>
+      <c r="I84">
+        <v>47.94</v>
+      </c>
+      <c r="J84">
+        <v>40.29</v>
+      </c>
+      <c r="K84">
+        <v>33.58</v>
+      </c>
+      <c r="L84">
+        <v>48.63</v>
+      </c>
+      <c r="M84">
+        <v>40.83</v>
+      </c>
+      <c r="N84">
+        <v>-116.88</v>
+      </c>
+      <c r="O84">
+        <v>-110.94</v>
+      </c>
+      <c r="P84">
+        <v>-113.67</v>
+      </c>
+      <c r="Q84">
+        <v>-25.69</v>
+      </c>
+      <c r="R84">
+        <v>-19.25</v>
+      </c>
+      <c r="S84">
+        <v>-22.29</v>
+      </c>
+      <c r="T84">
+        <v>-14.63</v>
+      </c>
+      <c r="U84">
+        <v>-6.94</v>
+      </c>
+      <c r="V84">
+        <v>-10.57</v>
+      </c>
+    </row>
+    <row r="85" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A85" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B85" s="2">
+        <v>251107</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E85" s="2">
+        <v>37.550910000000002</v>
+      </c>
+      <c r="F85" s="2">
+        <v>126.99139</v>
+      </c>
+      <c r="G85" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H85">
+        <v>30.5</v>
+      </c>
+      <c r="I85">
+        <v>45.77</v>
+      </c>
+      <c r="J85">
+        <v>41.08</v>
+      </c>
+      <c r="K85">
+        <v>37.159999999999997</v>
+      </c>
+      <c r="L85">
+        <v>45.77</v>
+      </c>
+      <c r="M85">
+        <v>43.33</v>
+      </c>
+      <c r="N85">
+        <v>-113.57</v>
+      </c>
+      <c r="O85">
+        <v>-110.88</v>
+      </c>
+      <c r="P85">
+        <v>-112.35</v>
+      </c>
+      <c r="Q85">
+        <v>-26.75</v>
+      </c>
+      <c r="R85">
+        <v>-19.82</v>
+      </c>
+      <c r="S85">
+        <v>-22.97</v>
+      </c>
+      <c r="T85">
+        <v>-14.94</v>
+      </c>
+      <c r="U85">
+        <v>-7.63</v>
+      </c>
+      <c r="V85">
+        <v>-10.89</v>
+      </c>
+    </row>
+    <row r="86" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A86" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B86" s="2">
+        <v>251107</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E86" s="2">
+        <v>37.550910000000002</v>
+      </c>
+      <c r="F86" s="2">
+        <v>126.99139</v>
+      </c>
+      <c r="G86" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H86">
+        <v>33.93</v>
+      </c>
+      <c r="I86">
+        <v>47.35</v>
+      </c>
+      <c r="J86">
+        <v>41.26</v>
+      </c>
+      <c r="K86">
+        <v>35.72</v>
+      </c>
+      <c r="L86">
+        <v>47.35</v>
+      </c>
+      <c r="M86">
+        <v>43.67</v>
+      </c>
+      <c r="N86">
+        <v>0</v>
+      </c>
+      <c r="O86">
+        <v>0</v>
+      </c>
+      <c r="P86">
+        <v>0</v>
+      </c>
+      <c r="Q86">
+        <v>0</v>
+      </c>
+      <c r="R86">
+        <v>0</v>
+      </c>
+      <c r="S86">
+        <v>0</v>
+      </c>
+      <c r="T86">
+        <v>0</v>
+      </c>
+      <c r="U86">
+        <v>0</v>
+      </c>
+      <c r="V86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A87" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B87" s="2">
+        <v>251107</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E87" s="2">
+        <v>37.551589999999997</v>
+      </c>
+      <c r="F87" s="2">
+        <v>126.98927999999999</v>
+      </c>
+      <c r="G87" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H87">
+        <v>43.03</v>
+      </c>
+      <c r="I87">
+        <v>61.6</v>
+      </c>
+      <c r="J87">
+        <v>53.76</v>
+      </c>
+      <c r="K87">
+        <v>43.03</v>
+      </c>
+      <c r="L87">
+        <v>61.6</v>
+      </c>
+      <c r="M87">
+        <v>55.35</v>
+      </c>
+      <c r="N87">
+        <v>-92.69</v>
+      </c>
+      <c r="O87">
+        <v>-85</v>
+      </c>
+      <c r="P87">
+        <v>-88.26</v>
+      </c>
+      <c r="Q87">
+        <v>-11.32</v>
+      </c>
+      <c r="R87">
+        <v>-10.44</v>
+      </c>
+      <c r="S87">
+        <v>-10.86</v>
+      </c>
+      <c r="T87">
+        <v>9.56</v>
+      </c>
+      <c r="U87">
+        <v>16.12</v>
+      </c>
+      <c r="V87">
+        <v>13.04</v>
+      </c>
+    </row>
+    <row r="88" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A88" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B88" s="2">
+        <v>251107</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E88" s="2">
+        <v>37.551589999999997</v>
+      </c>
+      <c r="F88" s="2">
+        <v>126.98927999999999</v>
+      </c>
+      <c r="G88" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H88">
+        <v>39.47</v>
+      </c>
+      <c r="I88">
+        <v>64.58</v>
+      </c>
+      <c r="J88">
+        <v>52.19</v>
+      </c>
+      <c r="K88">
+        <v>39.47</v>
+      </c>
+      <c r="L88">
+        <v>64.58</v>
+      </c>
+      <c r="M88">
+        <v>53.61</v>
+      </c>
+      <c r="N88">
+        <v>-90</v>
+      </c>
+      <c r="O88">
+        <v>-85.82</v>
+      </c>
+      <c r="P88">
+        <v>-88.15</v>
+      </c>
+      <c r="Q88">
+        <v>-11.13</v>
+      </c>
+      <c r="R88">
+        <v>-10.25</v>
+      </c>
+      <c r="S88">
+        <v>-10.62</v>
+      </c>
+      <c r="T88">
+        <v>9.6199999999999992</v>
+      </c>
+      <c r="U88">
+        <v>15.43</v>
+      </c>
+      <c r="V88">
+        <v>12.8</v>
+      </c>
+    </row>
+    <row r="89" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A89" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B89" s="2">
+        <v>251107</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E89" s="2">
+        <v>37.551589999999997</v>
+      </c>
+      <c r="F89" s="2">
+        <v>126.98927999999999</v>
+      </c>
+      <c r="G89" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H89">
+        <v>45</v>
+      </c>
+      <c r="I89">
+        <v>58.87</v>
+      </c>
+      <c r="J89">
+        <v>52.33</v>
+      </c>
+      <c r="K89">
+        <v>45</v>
+      </c>
+      <c r="L89">
+        <v>58.87</v>
+      </c>
+      <c r="M89">
+        <v>52.12</v>
+      </c>
+      <c r="N89">
+        <v>-104.88</v>
+      </c>
+      <c r="O89">
+        <v>-101.88</v>
+      </c>
+      <c r="P89">
+        <v>-103.26</v>
+      </c>
+      <c r="Q89">
+        <v>-26.07</v>
+      </c>
+      <c r="R89">
+        <v>-21.94</v>
+      </c>
+      <c r="S89">
+        <v>-23.52</v>
+      </c>
+      <c r="T89">
+        <v>-14.82</v>
+      </c>
+      <c r="U89">
+        <v>-8.25</v>
+      </c>
+      <c r="V89">
+        <v>-11.76</v>
+      </c>
+    </row>
+    <row r="90" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A90" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B90" s="2">
+        <v>251107</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E90" s="2">
+        <v>37.551589999999997</v>
+      </c>
+      <c r="F90" s="2">
+        <v>126.98927999999999</v>
+      </c>
+      <c r="G90" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H90">
+        <v>46.39</v>
+      </c>
+      <c r="I90">
+        <v>68.97</v>
+      </c>
+      <c r="J90">
+        <v>57.56</v>
+      </c>
+      <c r="K90">
+        <v>46.39</v>
+      </c>
+      <c r="L90">
+        <v>61.35</v>
+      </c>
+      <c r="M90">
+        <v>55.65</v>
+      </c>
+      <c r="N90">
+        <v>0</v>
+      </c>
+      <c r="O90">
+        <v>0</v>
+      </c>
+      <c r="P90">
+        <v>0</v>
+      </c>
+      <c r="Q90">
+        <v>-23.13</v>
+      </c>
+      <c r="R90">
+        <v>-19.940000000000001</v>
+      </c>
+      <c r="S90">
+        <v>-21.43</v>
+      </c>
+      <c r="T90">
+        <v>0</v>
+      </c>
+      <c r="U90">
+        <v>0</v>
+      </c>
+      <c r="V90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A91" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B91" s="2">
+        <v>251107</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E91" s="2">
+        <v>37.551589999999997</v>
+      </c>
+      <c r="F91" s="2">
+        <v>126.98927999999999</v>
+      </c>
+      <c r="G91" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H91">
+        <v>47.14</v>
+      </c>
+      <c r="I91">
+        <v>64.56</v>
+      </c>
+      <c r="J91">
+        <v>57.49</v>
+      </c>
+      <c r="K91">
+        <v>40.43</v>
+      </c>
+      <c r="L91">
+        <v>64.56</v>
+      </c>
+      <c r="M91">
+        <v>54.1</v>
+      </c>
+      <c r="N91">
+        <v>-90.44</v>
+      </c>
+      <c r="O91">
+        <v>-86</v>
+      </c>
+      <c r="P91">
+        <v>-88.75</v>
+      </c>
+      <c r="Q91">
+        <v>-25.19</v>
+      </c>
+      <c r="R91">
+        <v>-21.57</v>
+      </c>
+      <c r="S91">
+        <v>-23</v>
+      </c>
+      <c r="T91">
+        <v>8.8699999999999992</v>
+      </c>
+      <c r="U91">
+        <v>14.31</v>
+      </c>
+      <c r="V91">
+        <v>11.34</v>
+      </c>
+    </row>
+    <row r="92" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A92" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B92" s="2">
+        <v>251107</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E92" s="2">
+        <v>37.55151</v>
+      </c>
+      <c r="F92" s="2">
+        <v>126.98952</v>
+      </c>
+      <c r="G92" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H92">
+        <v>39.83</v>
+      </c>
+      <c r="I92">
+        <v>57.9</v>
+      </c>
+      <c r="J92">
+        <v>44.72</v>
+      </c>
+      <c r="K92">
+        <v>39.83</v>
+      </c>
+      <c r="L92">
+        <v>57.9</v>
+      </c>
+      <c r="M92">
+        <v>45.58</v>
+      </c>
+      <c r="N92">
+        <v>-95.75</v>
+      </c>
+      <c r="O92">
+        <v>-88.5</v>
+      </c>
+      <c r="P92">
+        <v>-92.33</v>
+      </c>
+      <c r="Q92">
+        <v>-11.5</v>
+      </c>
+      <c r="R92">
+        <v>-9.94</v>
+      </c>
+      <c r="S92">
+        <v>-10.65</v>
+      </c>
+      <c r="T92">
+        <v>11.81</v>
+      </c>
+      <c r="U92">
+        <v>20.5</v>
+      </c>
+      <c r="V92">
+        <v>15.3</v>
+      </c>
+    </row>
+    <row r="93" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A93" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B93" s="2">
+        <v>251107</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E93" s="2">
+        <v>37.55151</v>
+      </c>
+      <c r="F93" s="2">
+        <v>126.98952</v>
+      </c>
+      <c r="G93" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H93">
+        <v>41.2</v>
+      </c>
+      <c r="I93">
+        <v>59.41</v>
+      </c>
+      <c r="J93">
+        <v>49.66</v>
+      </c>
+      <c r="K93">
+        <v>41.2</v>
+      </c>
+      <c r="L93">
+        <v>59.41</v>
+      </c>
+      <c r="M93">
+        <v>48.98</v>
+      </c>
+      <c r="N93">
+        <v>-93.07</v>
+      </c>
+      <c r="O93">
+        <v>-87.75</v>
+      </c>
+      <c r="P93">
+        <v>-90.27</v>
+      </c>
+      <c r="Q93">
+        <v>-11.25</v>
+      </c>
+      <c r="R93">
+        <v>-9.94</v>
+      </c>
+      <c r="S93">
+        <v>-10.41</v>
+      </c>
+      <c r="T93">
+        <v>11.87</v>
+      </c>
+      <c r="U93">
+        <v>18.62</v>
+      </c>
+      <c r="V93">
+        <v>15.01</v>
+      </c>
+    </row>
+    <row r="94" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A94" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B94" s="2">
+        <v>251107</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E94" s="2">
+        <v>37.55151</v>
+      </c>
+      <c r="F94" s="2">
+        <v>126.98952</v>
+      </c>
+      <c r="G94" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H94">
+        <v>38.630000000000003</v>
+      </c>
+      <c r="I94">
+        <v>54.05</v>
+      </c>
+      <c r="J94">
+        <v>47.39</v>
+      </c>
+      <c r="K94">
+        <v>41.95</v>
+      </c>
+      <c r="L94">
+        <v>54.05</v>
+      </c>
+      <c r="M94">
+        <v>47.63</v>
+      </c>
+      <c r="N94">
+        <v>-93.63</v>
+      </c>
+      <c r="O94">
+        <v>-89.69</v>
+      </c>
+      <c r="P94">
+        <v>-92.14</v>
+      </c>
+      <c r="Q94">
+        <v>-11.13</v>
+      </c>
+      <c r="R94">
+        <v>-9.5</v>
+      </c>
+      <c r="S94">
+        <v>-10.1</v>
+      </c>
+      <c r="T94">
+        <v>12.25</v>
+      </c>
+      <c r="U94">
+        <v>20.43</v>
+      </c>
+      <c r="V94">
+        <v>15.44</v>
+      </c>
+    </row>
+    <row r="95" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A95" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B95" s="2">
+        <v>251107</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E95" s="2">
+        <v>37.55151</v>
+      </c>
+      <c r="F95" s="2">
+        <v>126.98952</v>
+      </c>
+      <c r="G95" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H95">
+        <v>36.909999999999997</v>
+      </c>
+      <c r="I95">
+        <v>54.22</v>
+      </c>
+      <c r="J95">
+        <v>47.29</v>
+      </c>
+      <c r="K95">
+        <v>36.909999999999997</v>
+      </c>
+      <c r="L95">
+        <v>66.400000000000006</v>
+      </c>
+      <c r="M95">
+        <v>49.36</v>
+      </c>
+      <c r="N95">
+        <v>-92.94</v>
+      </c>
+      <c r="O95">
+        <v>-88.82</v>
+      </c>
+      <c r="P95">
+        <v>-91.3</v>
+      </c>
+      <c r="Q95">
+        <v>-11.38</v>
+      </c>
+      <c r="R95">
+        <v>-9.94</v>
+      </c>
+      <c r="S95">
+        <v>-10.69</v>
+      </c>
+      <c r="T95">
+        <v>12.25</v>
+      </c>
+      <c r="U95">
+        <v>22.75</v>
+      </c>
+      <c r="V95">
+        <v>15.84</v>
+      </c>
+    </row>
+    <row r="96" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A96" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B96" s="2">
+        <v>251107</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E96" s="2">
+        <v>37.55151</v>
+      </c>
+      <c r="F96" s="2">
+        <v>126.98952</v>
+      </c>
+      <c r="G96" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H96">
+        <v>40.9</v>
+      </c>
+      <c r="I96">
+        <v>61.88</v>
+      </c>
+      <c r="J96">
+        <v>46.1</v>
+      </c>
+      <c r="K96">
+        <v>41.02</v>
+      </c>
+      <c r="L96">
+        <v>61.88</v>
+      </c>
+      <c r="M96">
+        <v>47.7</v>
+      </c>
+      <c r="N96">
+        <v>-94.19</v>
+      </c>
+      <c r="O96">
+        <v>-91.32</v>
+      </c>
+      <c r="P96">
+        <v>-92.73</v>
+      </c>
+      <c r="Q96">
+        <v>-11.69</v>
+      </c>
+      <c r="R96">
+        <v>-9.75</v>
+      </c>
+      <c r="S96">
+        <v>-10.48</v>
+      </c>
+      <c r="T96">
+        <v>11.87</v>
+      </c>
+      <c r="U96">
+        <v>17.68</v>
+      </c>
+      <c r="V96">
+        <v>15.02</v>
+      </c>
+    </row>
+    <row r="97" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A97" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B97" s="2">
+        <v>251107</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D97" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E97" s="2">
+        <v>37.551490000000001</v>
+      </c>
+      <c r="F97" s="2">
+        <v>126.98994</v>
+      </c>
+      <c r="G97" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H97">
+        <v>26.61</v>
+      </c>
+      <c r="I97">
+        <v>34.93</v>
+      </c>
+      <c r="J97">
+        <v>31.76</v>
+      </c>
+      <c r="K97">
+        <v>26.72</v>
+      </c>
+      <c r="L97">
+        <v>34.93</v>
+      </c>
+      <c r="M97">
+        <v>31.65</v>
+      </c>
+      <c r="N97">
+        <v>-95.07</v>
+      </c>
+      <c r="O97">
+        <v>-91.07</v>
+      </c>
+      <c r="P97">
+        <v>-92.43</v>
+      </c>
+      <c r="Q97">
+        <v>-12.07</v>
+      </c>
+      <c r="R97">
+        <v>-11.07</v>
+      </c>
+      <c r="S97">
+        <v>-11.56</v>
+      </c>
+      <c r="T97">
+        <v>10.93</v>
+      </c>
+      <c r="U97">
+        <v>15.87</v>
+      </c>
+      <c r="V97">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="98" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A98" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B98" s="2">
+        <v>251107</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E98" s="2">
+        <v>37.551490000000001</v>
+      </c>
+      <c r="F98" s="2">
+        <v>126.98994</v>
+      </c>
+      <c r="G98" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H98">
+        <v>21.27</v>
+      </c>
+      <c r="I98">
+        <v>43.56</v>
+      </c>
+      <c r="J98">
+        <v>29.08</v>
+      </c>
+      <c r="K98">
+        <v>24.57</v>
+      </c>
+      <c r="L98">
+        <v>34.85</v>
+      </c>
+      <c r="M98">
+        <v>30.51</v>
+      </c>
+      <c r="N98">
+        <v>-98.57</v>
+      </c>
+      <c r="O98">
+        <v>-94.75</v>
+      </c>
+      <c r="P98">
+        <v>-96.38</v>
+      </c>
+      <c r="Q98">
+        <v>-12.07</v>
+      </c>
+      <c r="R98">
+        <v>-10.5</v>
+      </c>
+      <c r="S98">
+        <v>-11.23</v>
+      </c>
+      <c r="T98">
+        <v>9.5</v>
+      </c>
+      <c r="U98">
+        <v>15.5</v>
+      </c>
+      <c r="V98">
+        <v>12.47</v>
+      </c>
+    </row>
+    <row r="99" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A99" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B99" s="2">
+        <v>251107</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D99" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E99" s="2">
+        <v>37.551490000000001</v>
+      </c>
+      <c r="F99" s="2">
+        <v>126.98994</v>
+      </c>
+      <c r="G99" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H99">
+        <v>27.51</v>
+      </c>
+      <c r="I99">
+        <v>34.89</v>
+      </c>
+      <c r="J99">
+        <v>32.270000000000003</v>
+      </c>
+      <c r="K99">
+        <v>30.25</v>
+      </c>
+      <c r="L99">
+        <v>36.07</v>
+      </c>
+      <c r="M99">
+        <v>33.31</v>
+      </c>
+      <c r="N99">
+        <v>-111.07</v>
+      </c>
+      <c r="O99">
+        <v>-108</v>
+      </c>
+      <c r="P99">
+        <v>-109.84</v>
+      </c>
+      <c r="Q99">
+        <v>-27.25</v>
+      </c>
+      <c r="R99">
+        <v>-19.75</v>
+      </c>
+      <c r="S99">
+        <v>-23.94</v>
+      </c>
+      <c r="T99">
+        <v>-14.07</v>
+      </c>
+      <c r="U99">
+        <v>-7</v>
+      </c>
+      <c r="V99">
+        <v>-11.17</v>
+      </c>
+    </row>
+    <row r="100" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A100" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B100" s="2">
+        <v>251107</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E100" s="2">
+        <v>37.551490000000001</v>
+      </c>
+      <c r="F100" s="2">
+        <v>126.98994</v>
+      </c>
+      <c r="G100" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H100">
+        <v>24.05</v>
+      </c>
+      <c r="I100">
+        <v>32.32</v>
+      </c>
+      <c r="J100">
+        <v>29.74</v>
+      </c>
+      <c r="K100">
+        <v>24.05</v>
+      </c>
+      <c r="L100">
+        <v>33.11</v>
+      </c>
+      <c r="M100">
+        <v>29.29</v>
+      </c>
+      <c r="N100">
+        <v>-97.44</v>
+      </c>
+      <c r="O100">
+        <v>-94.57</v>
+      </c>
+      <c r="P100">
+        <v>-95.66</v>
+      </c>
+      <c r="Q100">
+        <v>-12.57</v>
+      </c>
+      <c r="R100">
+        <v>-11.88</v>
+      </c>
+      <c r="S100">
+        <v>-12.28</v>
+      </c>
+      <c r="T100">
+        <v>9.81</v>
+      </c>
+      <c r="U100">
+        <v>12.75</v>
+      </c>
+      <c r="V100">
+        <v>11.23</v>
+      </c>
+    </row>
+    <row r="101" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A101" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B101" s="2">
+        <v>251107</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E101" s="2">
+        <v>37.551490000000001</v>
+      </c>
+      <c r="F101" s="2">
+        <v>126.98994</v>
+      </c>
+      <c r="G101" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H101">
+        <v>27.46</v>
+      </c>
+      <c r="I101">
+        <v>35.57</v>
+      </c>
+      <c r="J101">
+        <v>32.450000000000003</v>
+      </c>
+      <c r="K101">
+        <v>27.46</v>
+      </c>
+      <c r="L101">
+        <v>35.57</v>
+      </c>
+      <c r="M101">
+        <v>32.520000000000003</v>
+      </c>
+      <c r="N101">
+        <v>-97.13</v>
+      </c>
+      <c r="O101">
+        <v>-93.82</v>
+      </c>
+      <c r="P101">
+        <v>-95.62</v>
+      </c>
+      <c r="Q101">
+        <v>-12.5</v>
+      </c>
+      <c r="R101">
+        <v>-11.5</v>
+      </c>
+      <c r="S101">
+        <v>-12.16</v>
+      </c>
+      <c r="T101">
+        <v>9.31</v>
+      </c>
+      <c r="U101">
+        <v>12.5</v>
+      </c>
+      <c r="V101">
+        <v>10.66</v>
+      </c>
+    </row>
+    <row r="102" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A102" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B102" s="2">
+        <v>251107</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E102" s="2">
+        <v>37.551349999999999</v>
+      </c>
+      <c r="F102" s="2">
+        <v>126.99042</v>
+      </c>
+      <c r="G102" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H102">
+        <v>36.369999999999997</v>
+      </c>
+      <c r="I102">
+        <v>45.68</v>
+      </c>
+      <c r="J102">
+        <v>42.5</v>
+      </c>
+      <c r="K102">
+        <v>27.89</v>
+      </c>
+      <c r="L102">
+        <v>45.18</v>
+      </c>
+      <c r="M102">
+        <v>38.92</v>
+      </c>
+      <c r="N102">
+        <v>-96.75</v>
+      </c>
+      <c r="O102">
+        <v>-95.07</v>
+      </c>
+      <c r="P102">
+        <v>-95.98</v>
+      </c>
+      <c r="Q102">
+        <v>-11.25</v>
+      </c>
+      <c r="R102">
+        <v>-10.75</v>
+      </c>
+      <c r="S102">
+        <v>-10.97</v>
+      </c>
+      <c r="T102">
+        <v>9.75</v>
+      </c>
+      <c r="U102">
+        <v>13.37</v>
+      </c>
+      <c r="V102">
+        <v>11.67</v>
+      </c>
+    </row>
+    <row r="103" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A103" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B103" s="2">
+        <v>251107</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D103" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E103" s="2">
+        <v>37.551349999999999</v>
+      </c>
+      <c r="F103" s="2">
+        <v>126.99042</v>
+      </c>
+      <c r="G103" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H103">
+        <v>26.07</v>
+      </c>
+      <c r="I103">
+        <v>44.88</v>
+      </c>
+      <c r="J103">
+        <v>38.020000000000003</v>
+      </c>
+      <c r="K103">
+        <v>23.88</v>
+      </c>
+      <c r="L103">
+        <v>44.88</v>
+      </c>
+      <c r="M103">
+        <v>35.729999999999997</v>
+      </c>
+      <c r="N103">
+        <v>0</v>
+      </c>
+      <c r="O103">
+        <v>0</v>
+      </c>
+      <c r="P103">
+        <v>0</v>
+      </c>
+      <c r="Q103">
+        <v>0</v>
+      </c>
+      <c r="R103">
+        <v>0</v>
+      </c>
+      <c r="S103">
+        <v>0</v>
+      </c>
+      <c r="T103">
+        <v>0</v>
+      </c>
+      <c r="U103">
+        <v>0</v>
+      </c>
+      <c r="V103">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A104" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B104" s="2">
+        <v>251107</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D104" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E104" s="2">
+        <v>37.551349999999999</v>
+      </c>
+      <c r="F104" s="2">
+        <v>126.99042</v>
+      </c>
+      <c r="G104" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H104">
+        <v>27.06</v>
+      </c>
+      <c r="I104">
+        <v>40.89</v>
+      </c>
+      <c r="J104">
+        <v>35.26</v>
+      </c>
+      <c r="K104">
+        <v>22.74</v>
+      </c>
+      <c r="L104">
+        <v>38.68</v>
+      </c>
+      <c r="M104">
+        <v>31.9</v>
+      </c>
+      <c r="N104">
+        <v>0</v>
+      </c>
+      <c r="O104">
+        <v>0</v>
+      </c>
+      <c r="P104">
+        <v>0</v>
+      </c>
+      <c r="Q104">
+        <v>0</v>
+      </c>
+      <c r="R104">
+        <v>0</v>
+      </c>
+      <c r="S104">
+        <v>0</v>
+      </c>
+      <c r="T104">
+        <v>0</v>
+      </c>
+      <c r="U104">
+        <v>0</v>
+      </c>
+      <c r="V104">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A105" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B105" s="2">
+        <v>251107</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D105" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E105" s="2">
+        <v>37.551349999999999</v>
+      </c>
+      <c r="F105" s="2">
+        <v>126.99042</v>
+      </c>
+      <c r="G105" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H105">
+        <v>28.81</v>
+      </c>
+      <c r="I105">
+        <v>38.29</v>
+      </c>
+      <c r="J105">
+        <v>35</v>
+      </c>
+      <c r="K105">
+        <v>26.41</v>
+      </c>
+      <c r="L105">
+        <v>38.29</v>
+      </c>
+      <c r="M105">
+        <v>32.5</v>
+      </c>
+      <c r="N105">
+        <v>-97.5</v>
+      </c>
+      <c r="O105">
+        <v>-95.44</v>
+      </c>
+      <c r="P105">
+        <v>-96.47</v>
+      </c>
+      <c r="Q105">
+        <v>-11.13</v>
+      </c>
+      <c r="R105">
+        <v>-10.25</v>
+      </c>
+      <c r="S105">
+        <v>-10.62</v>
+      </c>
+      <c r="T105">
+        <v>9.5</v>
+      </c>
+      <c r="U105">
+        <v>13.56</v>
+      </c>
+      <c r="V105">
+        <v>11.91</v>
+      </c>
+    </row>
+    <row r="106" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A106" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B106" s="2">
+        <v>251107</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D106" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E106" s="2">
+        <v>37.551349999999999</v>
+      </c>
+      <c r="F106" s="2">
+        <v>126.99042</v>
+      </c>
+      <c r="G106" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H106">
+        <v>32.83</v>
+      </c>
+      <c r="I106">
+        <v>42.46</v>
+      </c>
+      <c r="J106">
+        <v>37.619999999999997</v>
+      </c>
+      <c r="K106">
+        <v>29.57</v>
+      </c>
+      <c r="L106">
+        <v>42.46</v>
+      </c>
+      <c r="M106">
+        <v>37.29</v>
+      </c>
+      <c r="N106">
+        <v>-99</v>
+      </c>
+      <c r="O106">
+        <v>-95.88</v>
+      </c>
+      <c r="P106">
+        <v>-97.37</v>
+      </c>
+      <c r="Q106">
+        <v>-11</v>
+      </c>
+      <c r="R106">
+        <v>-10.19</v>
+      </c>
+      <c r="S106">
+        <v>-10.61</v>
+      </c>
+      <c r="T106">
+        <v>9.25</v>
+      </c>
+      <c r="U106">
+        <v>12.5</v>
+      </c>
+      <c r="V106">
+        <v>11.16</v>
+      </c>
+    </row>
+    <row r="107" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A107" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B107" s="2">
+        <v>251107</v>
+      </c>
+      <c r="C107" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D107" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E107" s="2">
+        <v>37.551690000000001</v>
+      </c>
+      <c r="F107" s="2">
+        <v>126.98898</v>
+      </c>
+      <c r="G107" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H107">
+        <v>65.14</v>
+      </c>
+      <c r="I107">
+        <v>90.4</v>
+      </c>
+      <c r="J107">
+        <v>84.43</v>
+      </c>
+      <c r="K107">
+        <v>65.14</v>
+      </c>
+      <c r="L107">
+        <v>93.52</v>
+      </c>
+      <c r="M107">
+        <v>84.51</v>
+      </c>
+      <c r="N107">
+        <v>-79.13</v>
+      </c>
+      <c r="O107">
+        <v>-76.069999999999993</v>
+      </c>
+      <c r="P107">
+        <v>-77.23</v>
+      </c>
+      <c r="Q107">
+        <v>-10.75</v>
+      </c>
+      <c r="R107">
+        <v>-10.5</v>
+      </c>
+      <c r="S107">
+        <v>-10.64</v>
+      </c>
+      <c r="T107">
+        <v>19.18</v>
+      </c>
+      <c r="U107">
+        <v>21.75</v>
+      </c>
+      <c r="V107">
+        <v>20.37</v>
+      </c>
+    </row>
+    <row r="108" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A108" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B108" s="2">
+        <v>251107</v>
+      </c>
+      <c r="C108" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D108" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E108" s="2">
+        <v>37.551690000000001</v>
+      </c>
+      <c r="F108" s="2">
+        <v>126.98898</v>
+      </c>
+      <c r="G108" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H108">
+        <v>72.44</v>
+      </c>
+      <c r="I108">
+        <v>100.69</v>
+      </c>
+      <c r="J108">
+        <v>93.53</v>
+      </c>
+      <c r="K108">
+        <v>72.44</v>
+      </c>
+      <c r="L108">
+        <v>101.1</v>
+      </c>
+      <c r="M108">
+        <v>91.64</v>
+      </c>
+      <c r="N108">
+        <v>-81.44</v>
+      </c>
+      <c r="O108">
+        <v>-78.819999999999993</v>
+      </c>
+      <c r="P108">
+        <v>-79.7</v>
+      </c>
+      <c r="Q108">
+        <v>-10.75</v>
+      </c>
+      <c r="R108">
+        <v>-10.44</v>
+      </c>
+      <c r="S108">
+        <v>-10.59</v>
+      </c>
+      <c r="T108">
+        <v>17.87</v>
+      </c>
+      <c r="U108">
+        <v>22</v>
+      </c>
+      <c r="V108">
+        <v>19.78</v>
+      </c>
+    </row>
+    <row r="109" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A109" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B109" s="2">
+        <v>251107</v>
+      </c>
+      <c r="C109" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D109" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E109" s="2">
+        <v>37.551690000000001</v>
+      </c>
+      <c r="F109" s="2">
+        <v>126.98898</v>
+      </c>
+      <c r="G109" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H109">
+        <v>76.739999999999995</v>
+      </c>
+      <c r="I109">
+        <v>98.1</v>
+      </c>
+      <c r="J109">
+        <v>90.6</v>
+      </c>
+      <c r="K109">
+        <v>77.91</v>
+      </c>
+      <c r="L109">
+        <v>98.1</v>
+      </c>
+      <c r="M109">
+        <v>90.41</v>
+      </c>
+      <c r="N109">
+        <v>-83.63</v>
+      </c>
+      <c r="O109">
+        <v>-77.63</v>
+      </c>
+      <c r="P109">
+        <v>-79.84</v>
+      </c>
+      <c r="Q109">
+        <v>-10.82</v>
+      </c>
+      <c r="R109">
+        <v>-10.5</v>
+      </c>
+      <c r="S109">
+        <v>-10.7</v>
+      </c>
+      <c r="T109">
+        <v>16.25</v>
+      </c>
+      <c r="U109">
+        <v>20.68</v>
+      </c>
+      <c r="V109">
+        <v>18.48</v>
+      </c>
+    </row>
+    <row r="110" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A110" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B110" s="2">
+        <v>251107</v>
+      </c>
+      <c r="C110" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D110" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E110" s="2">
+        <v>37.551690000000001</v>
+      </c>
+      <c r="F110" s="2">
+        <v>126.98898</v>
+      </c>
+      <c r="G110" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H110">
+        <v>83.58</v>
+      </c>
+      <c r="I110">
+        <v>101.13</v>
+      </c>
+      <c r="J110">
+        <v>92.4</v>
+      </c>
+      <c r="K110">
+        <v>79.16</v>
+      </c>
+      <c r="L110">
+        <v>100.03</v>
+      </c>
+      <c r="M110">
+        <v>90.25</v>
+      </c>
+      <c r="N110">
+        <v>-80.69</v>
+      </c>
+      <c r="O110">
+        <v>-77.19</v>
+      </c>
+      <c r="P110">
+        <v>-78.63</v>
+      </c>
+      <c r="Q110">
+        <v>-10.75</v>
+      </c>
+      <c r="R110">
+        <v>-10.5</v>
+      </c>
+      <c r="S110">
+        <v>-10.64</v>
+      </c>
+      <c r="T110">
+        <v>18.37</v>
+      </c>
+      <c r="U110">
+        <v>22.81</v>
+      </c>
+      <c r="V110">
+        <v>20.25</v>
+      </c>
+    </row>
+    <row r="111" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A111" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B111" s="2">
+        <v>251107</v>
+      </c>
+      <c r="C111" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D111" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E111" s="2">
+        <v>37.551690000000001</v>
+      </c>
+      <c r="F111" s="2">
+        <v>126.98898</v>
+      </c>
+      <c r="G111" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H111">
+        <v>70.099999999999994</v>
+      </c>
+      <c r="I111">
+        <v>91.3</v>
+      </c>
+      <c r="J111">
+        <v>81.97</v>
+      </c>
+      <c r="K111">
+        <v>70.099999999999994</v>
+      </c>
+      <c r="L111">
+        <v>95.71</v>
+      </c>
+      <c r="M111">
+        <v>82.73</v>
+      </c>
+      <c r="N111">
+        <v>-80.44</v>
+      </c>
+      <c r="O111">
+        <v>-77.63</v>
+      </c>
+      <c r="P111">
+        <v>-78.84</v>
+      </c>
+      <c r="Q111">
+        <v>-10.82</v>
+      </c>
+      <c r="R111">
+        <v>-10.57</v>
+      </c>
+      <c r="S111">
+        <v>-10.71</v>
+      </c>
+      <c r="T111">
+        <v>17.059999999999999</v>
+      </c>
+      <c r="U111">
+        <v>20.12</v>
+      </c>
+      <c r="V111">
+        <v>18.7</v>
+      </c>
+    </row>
+    <row r="112" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A112" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B112" s="2">
+        <v>251107</v>
+      </c>
+      <c r="C112" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D112" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E112" s="2">
+        <v>37.551819999999999</v>
+      </c>
+      <c r="F112" s="2">
+        <v>126.98812</v>
+      </c>
+      <c r="G112" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H112">
+        <v>82.54</v>
+      </c>
+      <c r="I112">
+        <v>108.89</v>
+      </c>
+      <c r="J112">
+        <v>104.64</v>
+      </c>
+      <c r="K112">
+        <v>83.32</v>
+      </c>
+      <c r="L112">
+        <v>108.37</v>
+      </c>
+      <c r="M112">
+        <v>104.93</v>
+      </c>
+      <c r="N112">
+        <v>-57.63</v>
+      </c>
+      <c r="O112">
+        <v>-53.19</v>
+      </c>
+      <c r="P112">
+        <v>-54</v>
+      </c>
+      <c r="Q112">
+        <v>-10.75</v>
+      </c>
+      <c r="R112">
+        <v>-10.57</v>
+      </c>
+      <c r="S112">
+        <v>-10.68</v>
+      </c>
+      <c r="T112">
+        <v>20.62</v>
+      </c>
+      <c r="U112">
+        <v>22.87</v>
+      </c>
+      <c r="V112">
+        <v>21.55</v>
+      </c>
+    </row>
+    <row r="113" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A113" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B113" s="2">
+        <v>251107</v>
+      </c>
+      <c r="C113" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D113" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E113" s="2">
+        <v>37.551819999999999</v>
+      </c>
+      <c r="F113" s="2">
+        <v>126.98812</v>
+      </c>
+      <c r="G113" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H113">
+        <v>101.14</v>
+      </c>
+      <c r="I113">
+        <v>108.79</v>
+      </c>
+      <c r="J113">
+        <v>107.47</v>
+      </c>
+      <c r="K113">
+        <v>101.14</v>
+      </c>
+      <c r="L113">
+        <v>108.56</v>
+      </c>
+      <c r="M113">
+        <v>107.44</v>
+      </c>
+      <c r="N113">
+        <v>-57.63</v>
+      </c>
+      <c r="O113">
+        <v>-53.57</v>
+      </c>
+      <c r="P113">
+        <v>-54.71</v>
+      </c>
+      <c r="Q113">
+        <v>-10.82</v>
+      </c>
+      <c r="R113">
+        <v>-10.63</v>
+      </c>
+      <c r="S113">
+        <v>-10.7</v>
+      </c>
+      <c r="T113">
+        <v>20.25</v>
+      </c>
+      <c r="U113">
+        <v>22.5</v>
+      </c>
+      <c r="V113">
+        <v>21.2</v>
+      </c>
+    </row>
+    <row r="114" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A114" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B114" s="2">
+        <v>251107</v>
+      </c>
+      <c r="C114" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D114" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E114" s="2">
+        <v>37.551819999999999</v>
+      </c>
+      <c r="F114" s="2">
+        <v>126.98812</v>
+      </c>
+      <c r="G114" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H114">
+        <v>35.869999999999997</v>
+      </c>
+      <c r="I114">
+        <v>108.43</v>
+      </c>
+      <c r="J114">
+        <v>102.43</v>
+      </c>
+      <c r="K114">
+        <v>37.03</v>
+      </c>
+      <c r="L114">
+        <v>108.77</v>
+      </c>
+      <c r="M114">
+        <v>103.01</v>
+      </c>
+      <c r="N114">
+        <v>-60.88</v>
+      </c>
+      <c r="O114">
+        <v>-53.38</v>
+      </c>
+      <c r="P114">
+        <v>-55.58</v>
+      </c>
+      <c r="Q114">
+        <v>-10.82</v>
+      </c>
+      <c r="R114">
+        <v>-10.63</v>
+      </c>
+      <c r="S114">
+        <v>-10.7</v>
+      </c>
+      <c r="T114">
+        <v>20.25</v>
+      </c>
+      <c r="U114">
+        <v>23.37</v>
+      </c>
+      <c r="V114">
+        <v>21.37</v>
+      </c>
+    </row>
+    <row r="115" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A115" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B115" s="2">
+        <v>251107</v>
+      </c>
+      <c r="C115" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D115" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E115" s="2">
+        <v>37.551819999999999</v>
+      </c>
+      <c r="F115" s="2">
+        <v>126.98812</v>
+      </c>
+      <c r="G115" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H115">
+        <v>91.12</v>
+      </c>
+      <c r="I115">
+        <v>108.55</v>
+      </c>
+      <c r="J115">
+        <v>106.99</v>
+      </c>
+      <c r="K115">
+        <v>91.12</v>
+      </c>
+      <c r="L115">
+        <v>108.79</v>
+      </c>
+      <c r="M115">
+        <v>107.03</v>
+      </c>
+      <c r="N115">
+        <v>-58</v>
+      </c>
+      <c r="O115">
+        <v>-55.07</v>
+      </c>
+      <c r="P115">
+        <v>-57.38</v>
+      </c>
+      <c r="Q115">
+        <v>-10.88</v>
+      </c>
+      <c r="R115">
+        <v>-10.63</v>
+      </c>
+      <c r="S115">
+        <v>-10.75</v>
+      </c>
+      <c r="T115">
+        <v>19.559999999999999</v>
+      </c>
+      <c r="U115">
+        <v>22.31</v>
+      </c>
+      <c r="V115">
+        <v>20.72</v>
+      </c>
+    </row>
+    <row r="116" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A116" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B116" s="2">
+        <v>251107</v>
+      </c>
+      <c r="C116" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D116" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E116" s="2">
+        <v>37.551819999999999</v>
+      </c>
+      <c r="F116" s="2">
+        <v>126.98812</v>
+      </c>
+      <c r="G116" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H116">
+        <v>93.85</v>
+      </c>
+      <c r="I116">
+        <v>108.57</v>
+      </c>
+      <c r="J116">
+        <v>105.85</v>
+      </c>
+      <c r="K116">
+        <v>94.44</v>
+      </c>
+      <c r="L116">
+        <v>108.55</v>
+      </c>
+      <c r="M116">
+        <v>106.55</v>
+      </c>
+      <c r="N116">
+        <v>-56.75</v>
+      </c>
+      <c r="O116">
+        <v>-54.5</v>
+      </c>
+      <c r="P116">
+        <v>-55.36</v>
+      </c>
+      <c r="Q116">
+        <v>-10.75</v>
+      </c>
+      <c r="R116">
+        <v>-10.57</v>
+      </c>
+      <c r="S116">
+        <v>-10.66</v>
+      </c>
+      <c r="T116">
+        <v>20.43</v>
+      </c>
+      <c r="U116">
+        <v>24.62</v>
+      </c>
+      <c r="V116">
+        <v>21.74</v>
+      </c>
+    </row>
+    <row r="117" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A117" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B117" s="2">
+        <v>251107</v>
+      </c>
+      <c r="C117" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D117" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E117" s="2">
+        <v>37.550910000000002</v>
+      </c>
+      <c r="F117" s="2">
+        <v>126.99139</v>
+      </c>
+      <c r="G117" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H117">
+        <v>41.76</v>
+      </c>
+      <c r="I117">
+        <v>46.42</v>
+      </c>
+      <c r="J117">
+        <v>44.35</v>
+      </c>
+      <c r="K117">
+        <v>41.76</v>
+      </c>
+      <c r="L117">
+        <v>46.42</v>
+      </c>
+      <c r="M117">
+        <v>44.44</v>
+      </c>
+      <c r="N117">
+        <v>-90.13</v>
+      </c>
+      <c r="O117">
+        <v>-89</v>
+      </c>
+      <c r="P117">
+        <v>-89.51</v>
+      </c>
+      <c r="Q117">
+        <v>-11.19</v>
+      </c>
+      <c r="R117">
+        <v>-10.75</v>
+      </c>
+      <c r="S117">
+        <v>-10.97</v>
+      </c>
+      <c r="T117">
+        <v>13.25</v>
+      </c>
+      <c r="U117">
+        <v>17.93</v>
+      </c>
+      <c r="V117">
+        <v>16.86</v>
+      </c>
+    </row>
+    <row r="118" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A118" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B118" s="2">
+        <v>251107</v>
+      </c>
+      <c r="C118" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D118" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E118" s="2">
+        <v>37.550910000000002</v>
+      </c>
+      <c r="F118" s="2">
+        <v>126.99139</v>
+      </c>
+      <c r="G118" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H118">
+        <v>34.299999999999997</v>
+      </c>
+      <c r="I118">
+        <v>40.89</v>
+      </c>
+      <c r="J118">
+        <v>37.200000000000003</v>
+      </c>
+      <c r="K118">
+        <v>34.299999999999997</v>
+      </c>
+      <c r="L118">
+        <v>39.07</v>
+      </c>
+      <c r="M118">
+        <v>36.24</v>
+      </c>
+      <c r="N118">
+        <v>-97.07</v>
+      </c>
+      <c r="O118">
+        <v>-94.63</v>
+      </c>
+      <c r="P118">
+        <v>-95.96</v>
+      </c>
+      <c r="Q118">
+        <v>-11.75</v>
+      </c>
+      <c r="R118">
+        <v>-10.44</v>
+      </c>
+      <c r="S118">
+        <v>-11.27</v>
+      </c>
+      <c r="T118">
+        <v>10.119999999999999</v>
+      </c>
+      <c r="U118">
+        <v>13.56</v>
+      </c>
+      <c r="V118">
+        <v>12.09</v>
+      </c>
+    </row>
+    <row r="119" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A119" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B119" s="2">
+        <v>251107</v>
+      </c>
+      <c r="C119" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D119" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E119" s="2">
+        <v>37.550910000000002</v>
+      </c>
+      <c r="F119" s="2">
+        <v>126.99139</v>
+      </c>
+      <c r="G119" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H119">
+        <v>28.6</v>
+      </c>
+      <c r="I119">
+        <v>43.45</v>
+      </c>
+      <c r="J119">
+        <v>35.69</v>
+      </c>
+      <c r="K119">
+        <v>28.6</v>
+      </c>
+      <c r="L119">
+        <v>53.48</v>
+      </c>
+      <c r="M119">
+        <v>38.86</v>
+      </c>
+      <c r="N119">
+        <v>-105.07</v>
+      </c>
+      <c r="O119">
+        <v>-97.44</v>
+      </c>
+      <c r="P119">
+        <v>-101.55</v>
+      </c>
+      <c r="Q119">
+        <v>-12.19</v>
+      </c>
+      <c r="R119">
+        <v>-10.69</v>
+      </c>
+      <c r="S119">
+        <v>-11.37</v>
+      </c>
+      <c r="T119">
+        <v>5.75</v>
+      </c>
+      <c r="U119">
+        <v>12.87</v>
+      </c>
+      <c r="V119">
+        <v>9.26</v>
+      </c>
+    </row>
+    <row r="120" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A120" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B120" s="2">
+        <v>251107</v>
+      </c>
+      <c r="C120" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D120" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E120" s="2">
+        <v>37.550910000000002</v>
+      </c>
+      <c r="F120" s="2">
+        <v>126.99139</v>
+      </c>
+      <c r="G120" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H120">
+        <v>34.33</v>
+      </c>
+      <c r="I120">
+        <v>53.91</v>
+      </c>
+      <c r="J120">
+        <v>42.95</v>
+      </c>
+      <c r="K120">
+        <v>34.33</v>
+      </c>
+      <c r="L120">
+        <v>46.05</v>
+      </c>
+      <c r="M120">
+        <v>39.67</v>
+      </c>
+      <c r="N120">
+        <v>-98.07</v>
+      </c>
+      <c r="O120">
+        <v>-95.13</v>
+      </c>
+      <c r="P120">
+        <v>-96.68</v>
+      </c>
+      <c r="Q120">
+        <v>-11.38</v>
+      </c>
+      <c r="R120">
+        <v>-10.69</v>
+      </c>
+      <c r="S120">
+        <v>-11.01</v>
+      </c>
+      <c r="T120">
+        <v>13.87</v>
+      </c>
+      <c r="U120">
+        <v>17.62</v>
+      </c>
+      <c r="V120">
+        <v>15.84</v>
+      </c>
+    </row>
+    <row r="121" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A121" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B121" s="2">
+        <v>251107</v>
+      </c>
+      <c r="C121" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D121" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E121" s="2">
+        <v>37.550910000000002</v>
+      </c>
+      <c r="F121" s="2">
+        <v>126.99139</v>
+      </c>
+      <c r="G121" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H121">
+        <v>37.93</v>
+      </c>
+      <c r="I121">
+        <v>55.24</v>
+      </c>
+      <c r="J121">
+        <v>47.9</v>
+      </c>
+      <c r="K121">
+        <v>43.96</v>
+      </c>
+      <c r="L121">
+        <v>55.24</v>
+      </c>
+      <c r="M121">
+        <v>50.1</v>
+      </c>
+      <c r="N121">
+        <v>-94.75</v>
+      </c>
+      <c r="O121">
+        <v>-92.25</v>
+      </c>
+      <c r="P121">
+        <v>-93.83</v>
+      </c>
+      <c r="Q121">
+        <v>-11</v>
+      </c>
+      <c r="R121">
+        <v>-10.44</v>
+      </c>
+      <c r="S121">
+        <v>-10.74</v>
+      </c>
+      <c r="T121">
+        <v>15.25</v>
+      </c>
+      <c r="U121">
+        <v>21.62</v>
+      </c>
+      <c r="V121">
+        <v>16.600000000000001</v>
+      </c>
+    </row>
+    <row r="122" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A122" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B122" s="2">
+        <v>251107</v>
+      </c>
+      <c r="C122" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D122" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E122" s="2">
+        <v>37.551589999999997</v>
+      </c>
+      <c r="F122" s="2">
+        <v>126.98927999999999</v>
+      </c>
+      <c r="G122" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H122">
+        <v>62.97</v>
+      </c>
+      <c r="I122">
+        <v>73.040000000000006</v>
+      </c>
+      <c r="J122">
+        <v>70.290000000000006</v>
+      </c>
+      <c r="K122">
+        <v>62.97</v>
+      </c>
+      <c r="L122">
+        <v>73.040000000000006</v>
+      </c>
+      <c r="M122">
+        <v>69.63</v>
+      </c>
+      <c r="N122">
+        <v>-82</v>
+      </c>
+      <c r="O122">
+        <v>-78.94</v>
+      </c>
+      <c r="P122">
+        <v>-80.3</v>
+      </c>
+      <c r="Q122">
+        <v>-10.75</v>
+      </c>
+      <c r="R122">
+        <v>-10.5</v>
+      </c>
+      <c r="S122">
+        <v>-10.63</v>
+      </c>
+      <c r="T122">
+        <v>19.68</v>
+      </c>
+      <c r="U122">
+        <v>23.75</v>
+      </c>
+      <c r="V122">
+        <v>21.38</v>
+      </c>
+    </row>
+    <row r="123" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A123" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B123" s="2">
+        <v>251107</v>
+      </c>
+      <c r="C123" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D123" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E123" s="2">
+        <v>37.551589999999997</v>
+      </c>
+      <c r="F123" s="2">
+        <v>126.98927999999999</v>
+      </c>
+      <c r="G123" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H123">
+        <v>65.06</v>
+      </c>
+      <c r="I123">
+        <v>71.88</v>
+      </c>
+      <c r="J123">
+        <v>68.38</v>
+      </c>
+      <c r="K123">
+        <v>65.95</v>
+      </c>
+      <c r="L123">
+        <v>77.16</v>
+      </c>
+      <c r="M123">
+        <v>70.39</v>
+      </c>
+      <c r="N123">
+        <v>-84.44</v>
+      </c>
+      <c r="O123">
+        <v>-81.819999999999993</v>
+      </c>
+      <c r="P123">
+        <v>-83.07</v>
+      </c>
+      <c r="Q123">
+        <v>-10.63</v>
+      </c>
+      <c r="R123">
+        <v>-10.32</v>
+      </c>
+      <c r="S123">
+        <v>-10.48</v>
+      </c>
+      <c r="T123">
+        <v>18.87</v>
+      </c>
+      <c r="U123">
+        <v>25.12</v>
+      </c>
+      <c r="V123">
+        <v>21.64</v>
+      </c>
+    </row>
+    <row r="124" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A124" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B124" s="2">
+        <v>251107</v>
+      </c>
+      <c r="C124" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D124" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E124" s="2">
+        <v>37.551589999999997</v>
+      </c>
+      <c r="F124" s="2">
+        <v>126.98927999999999</v>
+      </c>
+      <c r="G124" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H124">
+        <v>57.19</v>
+      </c>
+      <c r="I124">
+        <v>75.819999999999993</v>
+      </c>
+      <c r="J124">
+        <v>68.8</v>
+      </c>
+      <c r="K124">
+        <v>60.34</v>
+      </c>
+      <c r="L124">
+        <v>74.14</v>
+      </c>
+      <c r="M124">
+        <v>68.540000000000006</v>
+      </c>
+      <c r="N124">
+        <v>-84.63</v>
+      </c>
+      <c r="O124">
+        <v>-80.69</v>
+      </c>
+      <c r="P124">
+        <v>-82.56</v>
+      </c>
+      <c r="Q124">
+        <v>-10.75</v>
+      </c>
+      <c r="R124">
+        <v>-10.32</v>
+      </c>
+      <c r="S124">
+        <v>-10.53</v>
+      </c>
+      <c r="T124">
+        <v>19.809999999999999</v>
+      </c>
+      <c r="U124">
+        <v>25.43</v>
+      </c>
+      <c r="V124">
+        <v>21.95</v>
+      </c>
+    </row>
+    <row r="125" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A125" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B125" s="2">
+        <v>251107</v>
+      </c>
+      <c r="C125" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D125" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E125" s="2">
+        <v>37.551589999999997</v>
+      </c>
+      <c r="F125" s="2">
+        <v>126.98927999999999</v>
+      </c>
+      <c r="G125" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H125">
+        <v>61.41</v>
+      </c>
+      <c r="I125">
+        <v>71.7</v>
+      </c>
+      <c r="J125">
+        <v>67.180000000000007</v>
+      </c>
+      <c r="K125">
+        <v>61.41</v>
+      </c>
+      <c r="L125">
+        <v>71.08</v>
+      </c>
+      <c r="M125">
+        <v>66.84</v>
+      </c>
+      <c r="N125">
+        <v>-83.94</v>
+      </c>
+      <c r="O125">
+        <v>-79.75</v>
+      </c>
+      <c r="P125">
+        <v>-81.92</v>
+      </c>
+      <c r="Q125">
+        <v>-10.69</v>
+      </c>
+      <c r="R125">
+        <v>-10.32</v>
+      </c>
+      <c r="S125">
+        <v>-10.46</v>
+      </c>
+      <c r="T125">
+        <v>19.809999999999999</v>
+      </c>
+      <c r="U125">
+        <v>25</v>
+      </c>
+      <c r="V125">
+        <v>22.21</v>
+      </c>
+    </row>
+    <row r="126" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A126" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B126" s="2">
+        <v>251107</v>
+      </c>
+      <c r="C126" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D126" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E126" s="2">
+        <v>37.551589999999997</v>
+      </c>
+      <c r="F126" s="2">
+        <v>126.98927999999999</v>
+      </c>
+      <c r="G126" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H126">
+        <v>67.38</v>
+      </c>
+      <c r="I126">
+        <v>78.290000000000006</v>
+      </c>
+      <c r="J126">
+        <v>73.540000000000006</v>
+      </c>
+      <c r="K126">
+        <v>65.23</v>
+      </c>
+      <c r="L126">
+        <v>78.290000000000006</v>
+      </c>
+      <c r="M126">
+        <v>72.59</v>
+      </c>
+      <c r="N126">
+        <v>-85.57</v>
+      </c>
+      <c r="O126">
+        <v>-81.25</v>
+      </c>
+      <c r="P126">
+        <v>-83.15</v>
+      </c>
+      <c r="Q126">
+        <v>-10.75</v>
+      </c>
+      <c r="R126">
+        <v>-10.38</v>
+      </c>
+      <c r="S126">
+        <v>-10.54</v>
+      </c>
+      <c r="T126">
+        <v>18.809999999999999</v>
+      </c>
+      <c r="U126">
+        <v>25.25</v>
+      </c>
+      <c r="V126">
+        <v>21.75</v>
+      </c>
+    </row>
+    <row r="127" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A127" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B127" s="2">
+        <v>251107</v>
+      </c>
+      <c r="C127" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D127" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E127" s="2">
+        <v>37.55151</v>
+      </c>
+      <c r="F127" s="2">
+        <v>126.98952</v>
+      </c>
+      <c r="G127" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H127">
+        <v>38.43</v>
+      </c>
+      <c r="I127">
+        <v>55.06</v>
+      </c>
+      <c r="J127">
+        <v>49.73</v>
+      </c>
+      <c r="K127">
+        <v>39.81</v>
+      </c>
+      <c r="L127">
+        <v>55.06</v>
+      </c>
+      <c r="M127">
+        <v>51.46</v>
+      </c>
+      <c r="N127">
+        <v>-91.5</v>
+      </c>
+      <c r="O127">
+        <v>-86.69</v>
+      </c>
+      <c r="P127">
+        <v>-88.62</v>
+      </c>
+      <c r="Q127">
+        <v>-10.25</v>
+      </c>
+      <c r="R127">
+        <v>-9.8800000000000008</v>
+      </c>
+      <c r="S127">
+        <v>-10.1</v>
+      </c>
+      <c r="T127">
+        <v>18.5</v>
+      </c>
+      <c r="U127">
+        <v>26.25</v>
+      </c>
+      <c r="V127">
+        <v>22.06</v>
+      </c>
+    </row>
+    <row r="128" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A128" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B128" s="2">
+        <v>251107</v>
+      </c>
+      <c r="C128" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D128" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E128" s="2">
+        <v>37.55151</v>
+      </c>
+      <c r="F128" s="2">
+        <v>126.98952</v>
+      </c>
+      <c r="G128" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H128">
+        <v>40.770000000000003</v>
+      </c>
+      <c r="I128">
+        <v>54.34</v>
+      </c>
+      <c r="J128">
+        <v>51.43</v>
+      </c>
+      <c r="K128">
+        <v>40.770000000000003</v>
+      </c>
+      <c r="L128">
+        <v>54.27</v>
+      </c>
+      <c r="M128">
+        <v>52.06</v>
+      </c>
+      <c r="N128">
+        <v>-86.88</v>
+      </c>
+      <c r="O128">
+        <v>-84.32</v>
+      </c>
+      <c r="P128">
+        <v>-85.68</v>
+      </c>
+      <c r="Q128">
+        <v>-10.25</v>
+      </c>
+      <c r="R128">
+        <v>-9.82</v>
+      </c>
+      <c r="S128">
+        <v>-10.029999999999999</v>
+      </c>
+      <c r="T128">
+        <v>21.43</v>
+      </c>
+      <c r="U128">
+        <v>26.31</v>
+      </c>
+      <c r="V128">
+        <v>25.55</v>
+      </c>
+    </row>
+    <row r="129" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A129" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B129" s="2">
+        <v>251107</v>
+      </c>
+      <c r="C129" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D129" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E129" s="2">
+        <v>37.55151</v>
+      </c>
+      <c r="F129" s="2">
+        <v>126.98952</v>
+      </c>
+      <c r="G129" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H129">
+        <v>50.29</v>
+      </c>
+      <c r="I129">
+        <v>54.34</v>
+      </c>
+      <c r="J129">
+        <v>52.94</v>
+      </c>
+      <c r="K129">
+        <v>50.5</v>
+      </c>
+      <c r="L129">
+        <v>54.33</v>
+      </c>
+      <c r="M129">
+        <v>53.38</v>
+      </c>
+      <c r="N129">
+        <v>-88.82</v>
+      </c>
+      <c r="O129">
+        <v>-86.07</v>
+      </c>
+      <c r="P129">
+        <v>-87.55</v>
+      </c>
+      <c r="Q129">
+        <v>-10.25</v>
+      </c>
+      <c r="R129">
+        <v>-9.82</v>
+      </c>
+      <c r="S129">
+        <v>-10.01</v>
+      </c>
+      <c r="T129">
+        <v>20.75</v>
+      </c>
+      <c r="U129">
+        <v>26.37</v>
+      </c>
+      <c r="V129">
+        <v>25.05</v>
+      </c>
+    </row>
+    <row r="130" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A130" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B130" s="2">
+        <v>251107</v>
+      </c>
+      <c r="C130" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D130" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E130" s="2">
+        <v>37.55151</v>
+      </c>
+      <c r="F130" s="2">
+        <v>126.98952</v>
+      </c>
+      <c r="G130" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H130">
+        <v>50.2</v>
+      </c>
+      <c r="I130">
+        <v>54.43</v>
+      </c>
+      <c r="J130">
+        <v>53.2</v>
+      </c>
+      <c r="K130">
+        <v>50.2</v>
+      </c>
+      <c r="L130">
+        <v>54.41</v>
+      </c>
+      <c r="M130">
+        <v>53.28</v>
+      </c>
+      <c r="N130">
+        <v>-88.57</v>
+      </c>
+      <c r="O130">
+        <v>-85.44</v>
+      </c>
+      <c r="P130">
+        <v>-86.97</v>
+      </c>
+      <c r="Q130">
+        <v>-10.25</v>
+      </c>
+      <c r="R130">
+        <v>-9.94</v>
+      </c>
+      <c r="S130">
+        <v>-10.07</v>
+      </c>
+      <c r="T130">
+        <v>20.87</v>
+      </c>
+      <c r="U130">
+        <v>26.31</v>
+      </c>
+      <c r="V130">
+        <v>25.4</v>
+      </c>
+    </row>
+    <row r="131" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A131" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B131" s="2">
+        <v>251107</v>
+      </c>
+      <c r="C131" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D131" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E131" s="2">
+        <v>37.55151</v>
+      </c>
+      <c r="F131" s="2">
+        <v>126.98952</v>
+      </c>
+      <c r="G131" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H131">
+        <v>51.28</v>
+      </c>
+      <c r="I131">
+        <v>54.36</v>
+      </c>
+      <c r="J131">
+        <v>53.58</v>
+      </c>
+      <c r="K131">
+        <v>38.44</v>
+      </c>
+      <c r="L131">
+        <v>54.36</v>
+      </c>
+      <c r="M131">
+        <v>51.74</v>
+      </c>
+      <c r="N131">
+        <v>-88</v>
+      </c>
+      <c r="O131">
+        <v>-84.82</v>
+      </c>
+      <c r="P131">
+        <v>-86.49</v>
+      </c>
+      <c r="Q131">
+        <v>-10.32</v>
+      </c>
+      <c r="R131">
+        <v>-9.94</v>
+      </c>
+      <c r="S131">
+        <v>-10.11</v>
+      </c>
+      <c r="T131">
+        <v>19.25</v>
+      </c>
+      <c r="U131">
+        <v>26.31</v>
+      </c>
+      <c r="V131">
+        <v>24.01</v>
+      </c>
+    </row>
+    <row r="132" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A132" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B132" s="2">
+        <v>251107</v>
+      </c>
+      <c r="C132" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D132" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E132" s="2">
+        <v>37.551490000000001</v>
+      </c>
+      <c r="F132" s="2">
+        <v>126.98994</v>
+      </c>
+      <c r="G132" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H132">
+        <v>27.29</v>
+      </c>
+      <c r="I132">
+        <v>32.479999999999997</v>
+      </c>
+      <c r="J132">
+        <v>29.59</v>
+      </c>
+      <c r="K132">
+        <v>27.29</v>
+      </c>
+      <c r="L132">
+        <v>30.64</v>
+      </c>
+      <c r="M132">
+        <v>29.21</v>
+      </c>
+      <c r="N132">
+        <v>-97.13</v>
+      </c>
+      <c r="O132">
+        <v>-93.07</v>
+      </c>
+      <c r="P132">
+        <v>-95.01</v>
+      </c>
+      <c r="Q132">
+        <v>-12.69</v>
+      </c>
+      <c r="R132">
+        <v>-10.75</v>
+      </c>
+      <c r="S132">
+        <v>-11.51</v>
+      </c>
+      <c r="T132">
+        <v>5.87</v>
+      </c>
+      <c r="U132">
+        <v>11</v>
+      </c>
+      <c r="V132">
+        <v>9.31</v>
+      </c>
+    </row>
+    <row r="133" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A133" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B133" s="2">
+        <v>251107</v>
+      </c>
+      <c r="C133" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D133" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E133" s="2">
+        <v>37.551490000000001</v>
+      </c>
+      <c r="F133" s="2">
+        <v>126.98994</v>
+      </c>
+      <c r="G133" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H133">
+        <v>21.36</v>
+      </c>
+      <c r="I133">
+        <v>30.32</v>
+      </c>
+      <c r="J133">
+        <v>24.47</v>
+      </c>
+      <c r="K133">
+        <v>21.7</v>
+      </c>
+      <c r="L133">
+        <v>30.41</v>
+      </c>
+      <c r="M133">
+        <v>26.9</v>
+      </c>
+      <c r="N133">
+        <v>-95.32</v>
+      </c>
+      <c r="O133">
+        <v>-91.63</v>
+      </c>
+      <c r="P133">
+        <v>-94.04</v>
+      </c>
+      <c r="Q133">
+        <v>-11.69</v>
+      </c>
+      <c r="R133">
+        <v>-10.69</v>
+      </c>
+      <c r="S133">
+        <v>-11.16</v>
+      </c>
+      <c r="T133">
+        <v>8.31</v>
+      </c>
+      <c r="U133">
+        <v>13</v>
+      </c>
+      <c r="V133">
+        <v>9.91</v>
+      </c>
+    </row>
+    <row r="134" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A134" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B134" s="2">
+        <v>251107</v>
+      </c>
+      <c r="C134" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D134" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E134" s="2">
+        <v>37.551490000000001</v>
+      </c>
+      <c r="F134" s="2">
+        <v>126.98994</v>
+      </c>
+      <c r="G134" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H134">
+        <v>17.649999999999999</v>
+      </c>
+      <c r="I134">
+        <v>30.94</v>
+      </c>
+      <c r="J134">
+        <v>25.42</v>
+      </c>
+      <c r="K134">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="L134">
+        <v>28.63</v>
+      </c>
+      <c r="M134">
+        <v>25.73</v>
+      </c>
+      <c r="N134">
+        <v>-96.25</v>
+      </c>
+      <c r="O134">
+        <v>-92.82</v>
+      </c>
+      <c r="P134">
+        <v>-94.88</v>
+      </c>
+      <c r="Q134">
+        <v>-12</v>
+      </c>
+      <c r="R134">
+        <v>-10.82</v>
+      </c>
+      <c r="S134">
+        <v>-11.32</v>
+      </c>
+      <c r="T134">
+        <v>7.68</v>
+      </c>
+      <c r="U134">
+        <v>12.87</v>
+      </c>
+      <c r="V134">
+        <v>10.28</v>
+      </c>
+    </row>
+    <row r="135" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A135" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B135" s="2">
+        <v>251107</v>
+      </c>
+      <c r="C135" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D135" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E135" s="2">
+        <v>37.551490000000001</v>
+      </c>
+      <c r="F135" s="2">
+        <v>126.98994</v>
+      </c>
+      <c r="G135" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H135">
+        <v>24.99</v>
+      </c>
+      <c r="I135">
+        <v>32.4</v>
+      </c>
+      <c r="J135">
+        <v>27.78</v>
+      </c>
+      <c r="K135">
+        <v>24.99</v>
+      </c>
+      <c r="L135">
+        <v>32.950000000000003</v>
+      </c>
+      <c r="M135">
+        <v>29.06</v>
+      </c>
+      <c r="N135">
+        <v>-95.44</v>
+      </c>
+      <c r="O135">
+        <v>-92.32</v>
+      </c>
+      <c r="P135">
+        <v>-93.8</v>
+      </c>
+      <c r="Q135">
+        <v>-11.69</v>
+      </c>
+      <c r="R135">
+        <v>-10.25</v>
+      </c>
+      <c r="S135">
+        <v>-10.83</v>
+      </c>
+      <c r="T135">
+        <v>7.75</v>
+      </c>
+      <c r="U135">
+        <v>13.25</v>
+      </c>
+      <c r="V135">
+        <v>11.18</v>
+      </c>
+    </row>
+    <row r="136" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A136" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B136" s="2">
+        <v>251107</v>
+      </c>
+      <c r="C136" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D136" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E136" s="2">
+        <v>37.551490000000001</v>
+      </c>
+      <c r="F136" s="2">
+        <v>126.98994</v>
+      </c>
+      <c r="G136" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H136">
+        <v>22.19</v>
+      </c>
+      <c r="I136">
+        <v>32.520000000000003</v>
+      </c>
+      <c r="J136">
+        <v>29.2</v>
+      </c>
+      <c r="K136">
+        <v>26.4</v>
+      </c>
+      <c r="L136">
+        <v>30.96</v>
+      </c>
+      <c r="M136">
+        <v>29.26</v>
+      </c>
+      <c r="N136">
+        <v>-97.32</v>
+      </c>
+      <c r="O136">
+        <v>-93.57</v>
+      </c>
+      <c r="P136">
+        <v>-95.4</v>
+      </c>
+      <c r="Q136">
+        <v>-12</v>
+      </c>
+      <c r="R136">
+        <v>-10.38</v>
+      </c>
+      <c r="S136">
+        <v>-11.09</v>
+      </c>
+      <c r="T136">
+        <v>8.1199999999999992</v>
+      </c>
+      <c r="U136">
+        <v>12.25</v>
+      </c>
+      <c r="V136">
+        <v>9.9</v>
+      </c>
+    </row>
+    <row r="137" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A137" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B137" s="2">
+        <v>251107</v>
+      </c>
+      <c r="C137" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D137" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E137" s="2">
+        <v>37.551349999999999</v>
+      </c>
+      <c r="F137" s="2">
+        <v>126.99042</v>
+      </c>
+      <c r="G137" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H137">
+        <v>42.99</v>
+      </c>
+      <c r="I137">
+        <v>55.98</v>
+      </c>
+      <c r="J137">
+        <v>50.97</v>
+      </c>
+      <c r="K137">
+        <v>50.1</v>
+      </c>
+      <c r="L137">
+        <v>54.74</v>
+      </c>
+      <c r="M137">
+        <v>52.28</v>
+      </c>
+      <c r="N137">
+        <v>-98.88</v>
+      </c>
+      <c r="O137">
+        <v>-94.32</v>
+      </c>
+      <c r="P137">
+        <v>-96.66</v>
+      </c>
+      <c r="Q137">
+        <v>-10.44</v>
+      </c>
+      <c r="R137">
+        <v>-10</v>
+      </c>
+      <c r="S137">
+        <v>-10.199999999999999</v>
+      </c>
+      <c r="T137">
+        <v>13.18</v>
+      </c>
+      <c r="U137">
+        <v>18.12</v>
+      </c>
+      <c r="V137">
+        <v>15.84</v>
+      </c>
+    </row>
+    <row r="138" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A138" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B138" s="2">
+        <v>251107</v>
+      </c>
+      <c r="C138" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D138" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E138" s="2">
+        <v>37.551349999999999</v>
+      </c>
+      <c r="F138" s="2">
+        <v>126.99042</v>
+      </c>
+      <c r="G138" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H138">
+        <v>40.619999999999997</v>
+      </c>
+      <c r="I138">
+        <v>52.54</v>
+      </c>
+      <c r="J138">
+        <v>47.43</v>
+      </c>
+      <c r="K138">
+        <v>40.619999999999997</v>
+      </c>
+      <c r="L138">
+        <v>52.03</v>
+      </c>
+      <c r="M138">
+        <v>47.28</v>
+      </c>
+      <c r="N138">
+        <v>-98.38</v>
+      </c>
+      <c r="O138">
+        <v>-93.94</v>
+      </c>
+      <c r="P138">
+        <v>-97.17</v>
+      </c>
+      <c r="Q138">
+        <v>-10.63</v>
+      </c>
+      <c r="R138">
+        <v>-10.07</v>
+      </c>
+      <c r="S138">
+        <v>-10.35</v>
+      </c>
+      <c r="T138">
+        <v>12.62</v>
+      </c>
+      <c r="U138">
+        <v>16.559999999999999</v>
+      </c>
+      <c r="V138">
+        <v>14.81</v>
+      </c>
+    </row>
+    <row r="139" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A139" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B139" s="2">
+        <v>251107</v>
+      </c>
+      <c r="C139" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D139" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E139" s="2">
+        <v>37.551349999999999</v>
+      </c>
+      <c r="F139" s="2">
+        <v>126.99042</v>
+      </c>
+      <c r="G139" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H139">
+        <v>38.56</v>
+      </c>
+      <c r="I139">
+        <v>51.72</v>
+      </c>
+      <c r="J139">
+        <v>46.6</v>
+      </c>
+      <c r="K139">
+        <v>38.56</v>
+      </c>
+      <c r="L139">
+        <v>52.45</v>
+      </c>
+      <c r="M139">
+        <v>46.96</v>
+      </c>
+      <c r="N139">
+        <v>-98.75</v>
+      </c>
+      <c r="O139">
+        <v>-95.88</v>
+      </c>
+      <c r="P139">
+        <v>-97.12</v>
+      </c>
+      <c r="Q139">
+        <v>-10.38</v>
+      </c>
+      <c r="R139">
+        <v>-9.94</v>
+      </c>
+      <c r="S139">
+        <v>-10.16</v>
+      </c>
+      <c r="T139">
+        <v>13.93</v>
+      </c>
+      <c r="U139">
+        <v>17.43</v>
+      </c>
+      <c r="V139">
+        <v>15.55</v>
+      </c>
+    </row>
+    <row r="140" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A140" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B140" s="2">
+        <v>251107</v>
+      </c>
+      <c r="C140" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D140" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E140" s="2">
+        <v>37.551349999999999</v>
+      </c>
+      <c r="F140" s="2">
+        <v>126.99042</v>
+      </c>
+      <c r="G140" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H140">
+        <v>39.869999999999997</v>
+      </c>
+      <c r="I140">
+        <v>54.34</v>
+      </c>
+      <c r="J140">
+        <v>44.9</v>
+      </c>
+      <c r="K140">
+        <v>39.869999999999997</v>
+      </c>
+      <c r="L140">
+        <v>54.34</v>
+      </c>
+      <c r="M140">
+        <v>45.43</v>
+      </c>
+      <c r="N140">
+        <v>-97.32</v>
+      </c>
+      <c r="O140">
+        <v>-93.94</v>
+      </c>
+      <c r="P140">
+        <v>-94.87</v>
+      </c>
+      <c r="Q140">
+        <v>-10.57</v>
+      </c>
+      <c r="R140">
+        <v>-10.19</v>
+      </c>
+      <c r="S140">
+        <v>-10.4</v>
+      </c>
+      <c r="T140">
+        <v>16.059999999999999</v>
+      </c>
+      <c r="U140">
+        <v>19.93</v>
+      </c>
+      <c r="V140">
+        <v>17.739999999999998</v>
+      </c>
+    </row>
+    <row r="141" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A141" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B141" s="2">
+        <v>251107</v>
+      </c>
+      <c r="C141" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D141" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E141" s="2">
+        <v>37.551349999999999</v>
+      </c>
+      <c r="F141" s="2">
+        <v>126.99042</v>
+      </c>
+      <c r="G141" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H141">
+        <v>38.76</v>
+      </c>
+      <c r="I141">
+        <v>55.88</v>
+      </c>
+      <c r="J141">
+        <v>46.29</v>
+      </c>
+      <c r="K141">
+        <v>40.81</v>
+      </c>
+      <c r="L141">
+        <v>55.88</v>
+      </c>
+      <c r="M141">
+        <v>47.77</v>
+      </c>
+      <c r="N141">
+        <v>-101.57</v>
+      </c>
+      <c r="O141">
+        <v>-95.13</v>
+      </c>
+      <c r="P141">
+        <v>-98.2</v>
+      </c>
+      <c r="Q141">
+        <v>-10.63</v>
+      </c>
+      <c r="R141">
+        <v>-10.07</v>
+      </c>
+      <c r="S141">
+        <v>-10.34</v>
+      </c>
+      <c r="T141">
+        <v>12.43</v>
+      </c>
+      <c r="U141">
+        <v>16.43</v>
+      </c>
+      <c r="V141">
+        <v>14.43</v>
+      </c>
+    </row>
+    <row r="142" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A142" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B142" s="2">
+        <v>251107</v>
+      </c>
+      <c r="C142" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D142" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E142" s="2">
+        <v>37.551690000000001</v>
+      </c>
+      <c r="F142" s="2">
+        <v>126.98898</v>
+      </c>
+      <c r="G142" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H142">
+        <v>78.819999999999993</v>
+      </c>
+      <c r="I142">
+        <v>106.23</v>
+      </c>
+      <c r="J142">
+        <v>98.82</v>
+      </c>
+      <c r="K142">
+        <v>89.59</v>
+      </c>
+      <c r="L142">
+        <v>106.9</v>
+      </c>
+      <c r="M142">
+        <v>98.1</v>
+      </c>
+      <c r="N142">
+        <v>-89.75</v>
+      </c>
+      <c r="O142">
+        <v>-83.75</v>
+      </c>
+      <c r="P142">
+        <v>-86.12</v>
+      </c>
+      <c r="Q142">
+        <v>-11.32</v>
+      </c>
+      <c r="R142">
+        <v>-10.63</v>
+      </c>
+      <c r="S142">
+        <v>-10.9</v>
+      </c>
+      <c r="T142">
+        <v>11.37</v>
+      </c>
+      <c r="U142">
+        <v>18.18</v>
+      </c>
+      <c r="V142">
+        <v>15.67</v>
+      </c>
+    </row>
+    <row r="143" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A143" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B143" s="2">
+        <v>251107</v>
+      </c>
+      <c r="C143" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D143" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E143" s="2">
+        <v>37.551690000000001</v>
+      </c>
+      <c r="F143" s="2">
+        <v>126.98898</v>
+      </c>
+      <c r="G143" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H143">
+        <v>80.8</v>
+      </c>
+      <c r="I143">
+        <v>102.74</v>
+      </c>
+      <c r="J143">
+        <v>94.46</v>
+      </c>
+      <c r="K143">
+        <v>80.8</v>
+      </c>
+      <c r="L143">
+        <v>108.12</v>
+      </c>
+      <c r="M143">
+        <v>95.94</v>
+      </c>
+      <c r="N143">
+        <v>-90.25</v>
+      </c>
+      <c r="O143">
+        <v>-80.94</v>
+      </c>
+      <c r="P143">
+        <v>-84.45</v>
+      </c>
+      <c r="Q143">
+        <v>-11.38</v>
+      </c>
+      <c r="R143">
+        <v>-10.82</v>
+      </c>
+      <c r="S143">
+        <v>-11.01</v>
+      </c>
+      <c r="T143">
+        <v>12.87</v>
+      </c>
+      <c r="U143">
+        <v>18.559999999999999</v>
+      </c>
+      <c r="V143">
+        <v>15.64</v>
+      </c>
+    </row>
+    <row r="144" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A144" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B144" s="2">
+        <v>251107</v>
+      </c>
+      <c r="C144" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D144" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E144" s="2">
+        <v>37.551690000000001</v>
+      </c>
+      <c r="F144" s="2">
+        <v>126.98898</v>
+      </c>
+      <c r="G144" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H144">
+        <v>73.12</v>
+      </c>
+      <c r="I144">
+        <v>108.79</v>
+      </c>
+      <c r="J144">
+        <v>95.28</v>
+      </c>
+      <c r="K144">
+        <v>73.12</v>
+      </c>
+      <c r="L144">
+        <v>108.79</v>
+      </c>
+      <c r="M144">
+        <v>101.03</v>
+      </c>
+      <c r="N144">
+        <v>-90.19</v>
+      </c>
+      <c r="O144">
+        <v>-79.569999999999993</v>
+      </c>
+      <c r="P144">
+        <v>-85.16</v>
+      </c>
+      <c r="Q144">
+        <v>-11.25</v>
+      </c>
+      <c r="R144">
+        <v>-10.69</v>
+      </c>
+      <c r="S144">
+        <v>-10.93</v>
+      </c>
+      <c r="T144">
+        <v>12.18</v>
+      </c>
+      <c r="U144">
+        <v>18.43</v>
+      </c>
+      <c r="V144">
+        <v>15.86</v>
+      </c>
+    </row>
+    <row r="145" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A145" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B145" s="2">
+        <v>251107</v>
+      </c>
+      <c r="C145" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D145" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E145" s="2">
+        <v>37.551690000000001</v>
+      </c>
+      <c r="F145" s="2">
+        <v>126.98898</v>
+      </c>
+      <c r="G145" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H145">
+        <v>76.760000000000005</v>
+      </c>
+      <c r="I145">
+        <v>99.48</v>
+      </c>
+      <c r="J145">
+        <v>89.95</v>
+      </c>
+      <c r="K145">
+        <v>76.760000000000005</v>
+      </c>
+      <c r="L145">
+        <v>103.13</v>
+      </c>
+      <c r="M145">
+        <v>91.42</v>
+      </c>
+      <c r="N145">
+        <v>-86.63</v>
+      </c>
+      <c r="O145">
+        <v>-81.19</v>
+      </c>
+      <c r="P145">
+        <v>-83.47</v>
+      </c>
+      <c r="Q145">
+        <v>-11.25</v>
+      </c>
+      <c r="R145">
+        <v>-10.63</v>
+      </c>
+      <c r="S145">
+        <v>-10.92</v>
+      </c>
+      <c r="T145">
+        <v>11.93</v>
+      </c>
+      <c r="U145">
+        <v>17.309999999999999</v>
+      </c>
+      <c r="V145">
+        <v>14.84</v>
+      </c>
+    </row>
+    <row r="146" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A146" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B146" s="2">
+        <v>251107</v>
+      </c>
+      <c r="C146" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D146" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E146" s="2">
+        <v>37.551690000000001</v>
+      </c>
+      <c r="F146" s="2">
+        <v>126.98898</v>
+      </c>
+      <c r="G146" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H146">
+        <v>63.89</v>
+      </c>
+      <c r="I146">
+        <v>98.55</v>
+      </c>
+      <c r="J146">
+        <v>89.01</v>
+      </c>
+      <c r="K146">
+        <v>63.89</v>
+      </c>
+      <c r="L146">
+        <v>106.16</v>
+      </c>
+      <c r="M146">
+        <v>91.55</v>
+      </c>
+      <c r="N146">
+        <v>-89.94</v>
+      </c>
+      <c r="O146">
+        <v>-78.69</v>
+      </c>
+      <c r="P146">
+        <v>-84.12</v>
+      </c>
+      <c r="Q146">
+        <v>-11.57</v>
+      </c>
+      <c r="R146">
+        <v>-10.88</v>
+      </c>
+      <c r="S146">
+        <v>-11.13</v>
+      </c>
+      <c r="T146">
+        <v>10.5</v>
+      </c>
+      <c r="U146">
+        <v>18.059999999999999</v>
+      </c>
+      <c r="V146">
+        <v>13.94</v>
+      </c>
+    </row>
+    <row r="147" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A147" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B147" s="2">
+        <v>251107</v>
+      </c>
+      <c r="C147" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D147" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E147" s="2">
+        <v>37.551819999999999</v>
+      </c>
+      <c r="F147" s="2">
+        <v>126.98812</v>
+      </c>
+      <c r="G147" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H147">
+        <v>90.49</v>
+      </c>
+      <c r="I147">
+        <v>108.82</v>
+      </c>
+      <c r="J147">
+        <v>107.11</v>
+      </c>
+      <c r="K147">
+        <v>90.84</v>
+      </c>
+      <c r="L147">
+        <v>108.83</v>
+      </c>
+      <c r="M147">
+        <v>107.54</v>
+      </c>
+      <c r="N147">
+        <v>-71.69</v>
+      </c>
+      <c r="O147">
+        <v>-61.63</v>
+      </c>
+      <c r="P147">
+        <v>-66.430000000000007</v>
+      </c>
+      <c r="Q147">
+        <v>-11.07</v>
+      </c>
+      <c r="R147">
+        <v>-9.8800000000000008</v>
+      </c>
+      <c r="S147">
+        <v>-10.49</v>
+      </c>
+      <c r="T147">
+        <v>17.809999999999999</v>
+      </c>
+      <c r="U147">
+        <v>27</v>
+      </c>
+      <c r="V147">
+        <v>23.17</v>
+      </c>
+    </row>
+    <row r="148" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A148" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B148" s="2">
+        <v>251107</v>
+      </c>
+      <c r="C148" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D148" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E148" s="2">
+        <v>37.551819999999999</v>
+      </c>
+      <c r="F148" s="2">
+        <v>126.98812</v>
+      </c>
+      <c r="G148" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H148">
+        <v>90.53</v>
+      </c>
+      <c r="I148">
+        <v>108.97</v>
+      </c>
+      <c r="J148">
+        <v>107.93</v>
+      </c>
+      <c r="K148">
+        <v>90.53</v>
+      </c>
+      <c r="L148">
+        <v>108.84</v>
+      </c>
+      <c r="M148">
+        <v>107.82</v>
+      </c>
+      <c r="N148">
+        <v>-65.88</v>
+      </c>
+      <c r="O148">
+        <v>-62.38</v>
+      </c>
+      <c r="P148">
+        <v>-63.98</v>
+      </c>
+      <c r="Q148">
+        <v>-11.25</v>
+      </c>
+      <c r="R148">
+        <v>-10.130000000000001</v>
+      </c>
+      <c r="S148">
+        <v>-10.78</v>
+      </c>
+      <c r="T148">
+        <v>18.309999999999999</v>
+      </c>
+      <c r="U148">
+        <v>22.93</v>
+      </c>
+      <c r="V148">
+        <v>20.54</v>
+      </c>
+    </row>
+    <row r="149" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A149" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B149" s="2">
+        <v>251107</v>
+      </c>
+      <c r="C149" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D149" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E149" s="2">
+        <v>37.551819999999999</v>
+      </c>
+      <c r="F149" s="2">
+        <v>126.98812</v>
+      </c>
+      <c r="G149" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H149">
+        <v>105.84</v>
+      </c>
+      <c r="I149">
+        <v>108.83</v>
+      </c>
+      <c r="J149">
+        <v>108.23</v>
+      </c>
+      <c r="K149">
+        <v>105.84</v>
+      </c>
+      <c r="L149">
+        <v>108.82</v>
+      </c>
+      <c r="M149">
+        <v>108.14</v>
+      </c>
+      <c r="N149">
+        <v>-73.69</v>
+      </c>
+      <c r="O149">
+        <v>-60.19</v>
+      </c>
+      <c r="P149">
+        <v>-64.38</v>
+      </c>
+      <c r="Q149">
+        <v>-10.82</v>
+      </c>
+      <c r="R149">
+        <v>-10.44</v>
+      </c>
+      <c r="S149">
+        <v>-10.61</v>
+      </c>
+      <c r="T149">
+        <v>17.37</v>
+      </c>
+      <c r="U149">
+        <v>26.25</v>
+      </c>
+      <c r="V149">
+        <v>21.41</v>
+      </c>
+    </row>
+    <row r="150" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A150" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B150" s="2">
+        <v>251107</v>
+      </c>
+      <c r="C150" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D150" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E150" s="2">
+        <v>37.551819999999999</v>
+      </c>
+      <c r="F150" s="2">
+        <v>126.98812</v>
+      </c>
+      <c r="G150" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H150">
+        <v>104.2</v>
+      </c>
+      <c r="I150">
+        <v>108.97</v>
+      </c>
+      <c r="J150">
+        <v>108.36</v>
+      </c>
+      <c r="K150">
+        <v>104.2</v>
+      </c>
+      <c r="L150">
+        <v>108.82</v>
+      </c>
+      <c r="M150">
+        <v>108.32</v>
+      </c>
+      <c r="N150">
+        <v>-73.38</v>
+      </c>
+      <c r="O150">
+        <v>-60.88</v>
+      </c>
+      <c r="P150">
+        <v>-63.37</v>
+      </c>
+      <c r="Q150">
+        <v>-10.69</v>
+      </c>
+      <c r="R150">
+        <v>-10.32</v>
+      </c>
+      <c r="S150">
+        <v>-10.52</v>
+      </c>
+      <c r="T150">
+        <v>19.93</v>
+      </c>
+      <c r="U150">
+        <v>25.5</v>
+      </c>
+      <c r="V150">
+        <v>22.27</v>
+      </c>
+    </row>
+    <row r="151" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A151" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B151" s="2">
+        <v>251107</v>
+      </c>
+      <c r="C151" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D151" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E151" s="2">
+        <v>37.551819999999999</v>
+      </c>
+      <c r="F151" s="2">
+        <v>126.98812</v>
+      </c>
+      <c r="G151" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H151">
+        <v>103.2</v>
+      </c>
+      <c r="I151">
+        <v>108.82</v>
+      </c>
+      <c r="J151">
+        <v>108</v>
+      </c>
+      <c r="K151">
+        <v>108.04</v>
+      </c>
+      <c r="L151">
+        <v>108.82</v>
+      </c>
+      <c r="M151">
+        <v>108.57</v>
+      </c>
+      <c r="N151">
+        <v>-66.63</v>
+      </c>
+      <c r="O151">
+        <v>-59.69</v>
+      </c>
+      <c r="P151">
+        <v>-62.12</v>
+      </c>
+      <c r="Q151">
+        <v>-10.94</v>
+      </c>
+      <c r="R151">
+        <v>-10.38</v>
+      </c>
+      <c r="S151">
+        <v>-10.71</v>
+      </c>
+      <c r="T151">
+        <v>19</v>
+      </c>
+      <c r="U151">
+        <v>22.81</v>
+      </c>
+      <c r="V151">
+        <v>21.07</v>
+      </c>
+    </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
